--- a/examples/sequence/OUL/result/animal_id_indexed_result_data-5.xlsx
+++ b/examples/sequence/OUL/result/animal_id_indexed_result_data-5.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DC20"/>
+  <dimension ref="A1:CZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,11 @@
       <c r="G1" s="1" t="n"/>
       <c r="H1" s="1" t="n"/>
       <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>SecondsObserving</t>
+        </is>
+      </c>
       <c r="K1" s="1" t="n"/>
       <c r="L1" s="1" t="n"/>
       <c r="M1" s="1" t="n"/>
@@ -513,12 +517,12 @@
       <c r="AT1" s="1" t="n"/>
       <c r="AU1" s="1" t="n"/>
       <c r="AV1" s="1" t="n"/>
-      <c r="AW1" s="1" t="n"/>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>ObjectsInUpdatingLocationsUpdateTrial</t>
         </is>
       </c>
+      <c r="AX1" s="1" t="n"/>
       <c r="AY1" s="1" t="n"/>
       <c r="AZ1" s="1" t="n"/>
       <c r="BA1" s="1" t="n"/>
@@ -545,13 +549,13 @@
       <c r="BV1" s="1" t="n"/>
       <c r="BW1" s="1" t="n"/>
       <c r="BX1" s="1" t="n"/>
-      <c r="BY1" s="1" t="n"/>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>ObjectsInUpdatingLocationsTestTrial</t>
+        </is>
+      </c>
       <c r="BZ1" s="1" t="n"/>
-      <c r="CA1" s="1" t="inlineStr">
-        <is>
-          <t>ObjectsInUpdatingLocationsTestTrial</t>
-        </is>
-      </c>
+      <c r="CA1" s="1" t="n"/>
       <c r="CB1" s="1" t="n"/>
       <c r="CC1" s="1" t="n"/>
       <c r="CD1" s="1" t="n"/>
@@ -577,9 +581,6 @@
       <c r="CX1" s="1" t="n"/>
       <c r="CY1" s="1" t="n"/>
       <c r="CZ1" s="1" t="n"/>
-      <c r="DA1" s="1" t="n"/>
-      <c r="DB1" s="1" t="n"/>
-      <c r="DC1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -621,19 +622,59 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>SecondsObserving</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="n"/>
-      <c r="L2" s="1" t="n"/>
-      <c r="M2" s="1" t="n"/>
-      <c r="N2" s="1" t="n"/>
-      <c r="O2" s="1" t="n"/>
-      <c r="P2" s="1" t="n"/>
-      <c r="Q2" s="1" t="n"/>
-      <c r="R2" s="1" t="n"/>
-      <c r="S2" s="1" t="n"/>
-      <c r="T2" s="1" t="n"/>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>object_1</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>object_2</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>object_1</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>object_4</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>object_1</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>object_2</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>object_3</t>
+        </is>
+      </c>
+      <c r="T2" s="1" t="inlineStr">
+        <is>
+          <t>object_4</t>
+        </is>
+      </c>
       <c r="U2" s="1" t="inlineStr">
         <is>
           <t>All</t>
@@ -644,155 +685,140 @@
       <c r="X2" s="1" t="n"/>
       <c r="Y2" s="1" t="inlineStr">
         <is>
-          <t>Gaussian</t>
-        </is>
-      </c>
-      <c r="Z2" s="1" t="inlineStr">
-        <is>
           <t>Quadrant(1, 1)</t>
         </is>
       </c>
+      <c r="Z2" s="1" t="n"/>
       <c r="AA2" s="1" t="n"/>
       <c r="AB2" s="1" t="n"/>
       <c r="AC2" s="1" t="n"/>
       <c r="AD2" s="1" t="n"/>
-      <c r="AE2" s="1" t="n"/>
-      <c r="AF2" s="1" t="inlineStr">
+      <c r="AE2" s="1" t="inlineStr">
         <is>
           <t>Quadrant(1, 2)</t>
         </is>
       </c>
+      <c r="AF2" s="1" t="n"/>
       <c r="AG2" s="1" t="n"/>
       <c r="AH2" s="1" t="n"/>
       <c r="AI2" s="1" t="n"/>
       <c r="AJ2" s="1" t="n"/>
-      <c r="AK2" s="1" t="n"/>
-      <c r="AL2" s="1" t="inlineStr">
+      <c r="AK2" s="1" t="inlineStr">
         <is>
           <t>Quadrant(2, 1)</t>
         </is>
       </c>
+      <c r="AL2" s="1" t="n"/>
       <c r="AM2" s="1" t="n"/>
       <c r="AN2" s="1" t="n"/>
       <c r="AO2" s="1" t="n"/>
       <c r="AP2" s="1" t="n"/>
-      <c r="AQ2" s="1" t="n"/>
-      <c r="AR2" s="1" t="inlineStr">
+      <c r="AQ2" s="1" t="inlineStr">
         <is>
           <t>Quadrant(2, 2)</t>
         </is>
       </c>
+      <c r="AR2" s="1" t="n"/>
       <c r="AS2" s="1" t="n"/>
       <c r="AT2" s="1" t="n"/>
       <c r="AU2" s="1" t="n"/>
       <c r="AV2" s="1" t="n"/>
-      <c r="AW2" s="1" t="n"/>
-      <c r="AX2" s="1" t="inlineStr">
+      <c r="AW2" s="1" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
+      <c r="AX2" s="1" t="n"/>
       <c r="AY2" s="1" t="n"/>
       <c r="AZ2" s="1" t="n"/>
-      <c r="BA2" s="1" t="n"/>
-      <c r="BB2" s="1" t="inlineStr">
-        <is>
-          <t>Gaussian</t>
-        </is>
-      </c>
-      <c r="BC2" s="1" t="inlineStr">
+      <c r="BA2" s="1" t="inlineStr">
         <is>
           <t>Quadrant(1, 1)</t>
         </is>
       </c>
+      <c r="BB2" s="1" t="n"/>
+      <c r="BC2" s="1" t="n"/>
       <c r="BD2" s="1" t="n"/>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
-      <c r="BG2" s="1" t="n"/>
+      <c r="BG2" s="1" t="inlineStr">
+        <is>
+          <t>Quadrant(1, 2)</t>
+        </is>
+      </c>
       <c r="BH2" s="1" t="n"/>
-      <c r="BI2" s="1" t="inlineStr">
-        <is>
-          <t>Quadrant(1, 2)</t>
-        </is>
-      </c>
+      <c r="BI2" s="1" t="n"/>
       <c r="BJ2" s="1" t="n"/>
       <c r="BK2" s="1" t="n"/>
       <c r="BL2" s="1" t="n"/>
-      <c r="BM2" s="1" t="n"/>
+      <c r="BM2" s="1" t="inlineStr">
+        <is>
+          <t>Quadrant(2, 1)</t>
+        </is>
+      </c>
       <c r="BN2" s="1" t="n"/>
-      <c r="BO2" s="1" t="inlineStr">
-        <is>
-          <t>Quadrant(2, 1)</t>
-        </is>
-      </c>
+      <c r="BO2" s="1" t="n"/>
       <c r="BP2" s="1" t="n"/>
       <c r="BQ2" s="1" t="n"/>
       <c r="BR2" s="1" t="n"/>
-      <c r="BS2" s="1" t="n"/>
+      <c r="BS2" s="1" t="inlineStr">
+        <is>
+          <t>Quadrant(2, 2)</t>
+        </is>
+      </c>
       <c r="BT2" s="1" t="n"/>
-      <c r="BU2" s="1" t="inlineStr">
-        <is>
-          <t>Quadrant(2, 2)</t>
-        </is>
-      </c>
+      <c r="BU2" s="1" t="n"/>
       <c r="BV2" s="1" t="n"/>
       <c r="BW2" s="1" t="n"/>
       <c r="BX2" s="1" t="n"/>
-      <c r="BY2" s="1" t="n"/>
+      <c r="BY2" s="1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
       <c r="BZ2" s="1" t="n"/>
-      <c r="CA2" s="1" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
+      <c r="CA2" s="1" t="n"/>
       <c r="CB2" s="1" t="n"/>
-      <c r="CC2" s="1" t="n"/>
+      <c r="CC2" s="1" t="inlineStr">
+        <is>
+          <t>Quadrant(1, 1)</t>
+        </is>
+      </c>
       <c r="CD2" s="1" t="n"/>
-      <c r="CE2" s="1" t="inlineStr">
-        <is>
-          <t>Gaussian</t>
-        </is>
-      </c>
-      <c r="CF2" s="1" t="inlineStr">
-        <is>
-          <t>Quadrant(1, 1)</t>
-        </is>
-      </c>
+      <c r="CE2" s="1" t="n"/>
+      <c r="CF2" s="1" t="n"/>
       <c r="CG2" s="1" t="n"/>
       <c r="CH2" s="1" t="n"/>
-      <c r="CI2" s="1" t="n"/>
+      <c r="CI2" s="1" t="inlineStr">
+        <is>
+          <t>Quadrant(1, 2)</t>
+        </is>
+      </c>
       <c r="CJ2" s="1" t="n"/>
       <c r="CK2" s="1" t="n"/>
-      <c r="CL2" s="1" t="inlineStr">
-        <is>
-          <t>Quadrant(1, 2)</t>
-        </is>
-      </c>
+      <c r="CL2" s="1" t="n"/>
       <c r="CM2" s="1" t="n"/>
       <c r="CN2" s="1" t="n"/>
-      <c r="CO2" s="1" t="n"/>
+      <c r="CO2" s="1" t="inlineStr">
+        <is>
+          <t>Quadrant(2, 1)</t>
+        </is>
+      </c>
       <c r="CP2" s="1" t="n"/>
       <c r="CQ2" s="1" t="n"/>
-      <c r="CR2" s="1" t="inlineStr">
-        <is>
-          <t>Quadrant(2, 1)</t>
-        </is>
-      </c>
+      <c r="CR2" s="1" t="n"/>
       <c r="CS2" s="1" t="n"/>
       <c r="CT2" s="1" t="n"/>
-      <c r="CU2" s="1" t="n"/>
+      <c r="CU2" s="1" t="inlineStr">
+        <is>
+          <t>Quadrant(2, 2)</t>
+        </is>
+      </c>
       <c r="CV2" s="1" t="n"/>
       <c r="CW2" s="1" t="n"/>
-      <c r="CX2" s="1" t="inlineStr">
-        <is>
-          <t>Quadrant(2, 2)</t>
-        </is>
-      </c>
+      <c r="CX2" s="1" t="n"/>
       <c r="CY2" s="1" t="n"/>
       <c r="CZ2" s="1" t="n"/>
-      <c r="DA2" s="1" t="n"/>
-      <c r="DB2" s="1" t="n"/>
-      <c r="DC2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -834,61 +860,17 @@
           <t>all</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>object_1</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>object_2</t>
-        </is>
-      </c>
-      <c r="M3" s="1" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="N3" s="1" t="inlineStr">
-        <is>
-          <t>object_1</t>
-        </is>
-      </c>
-      <c r="O3" s="1" t="inlineStr">
-        <is>
-          <t>object_4</t>
-        </is>
-      </c>
-      <c r="P3" s="1" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="Q3" s="1" t="inlineStr">
-        <is>
-          <t>object_1</t>
-        </is>
-      </c>
-      <c r="R3" s="1" t="inlineStr">
-        <is>
-          <t>object_2</t>
-        </is>
-      </c>
-      <c r="S3" s="1" t="inlineStr">
-        <is>
-          <t>object_3</t>
-        </is>
-      </c>
-      <c r="T3" s="1" t="inlineStr">
-        <is>
-          <t>object_4</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr"/>
+      <c r="L3" s="1" t="inlineStr"/>
+      <c r="M3" s="1" t="inlineStr"/>
+      <c r="N3" s="1" t="inlineStr"/>
+      <c r="O3" s="1" t="inlineStr"/>
+      <c r="P3" s="1" t="inlineStr"/>
+      <c r="Q3" s="1" t="inlineStr"/>
+      <c r="R3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr"/>
+      <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr">
         <is>
           <t>Displacement</t>
@@ -911,415 +893,400 @@
       </c>
       <c r="Y3" s="1" t="inlineStr">
         <is>
-          <t>CenterToPeriphery</t>
+          <t>Displacement</t>
         </is>
       </c>
       <c r="Z3" s="1" t="inlineStr">
         <is>
+          <t>MedianSpeed</t>
+        </is>
+      </c>
+      <c r="AA3" s="1" t="inlineStr">
+        <is>
+          <t>MedianAcceleration</t>
+        </is>
+      </c>
+      <c r="AB3" s="1" t="inlineStr">
+        <is>
+          <t>FreezingTime</t>
+        </is>
+      </c>
+      <c r="AC3" s="1" t="inlineStr">
+        <is>
+          <t>Entries</t>
+        </is>
+      </c>
+      <c r="AD3" s="1" t="inlineStr">
+        <is>
+          <t>SecondsPresent</t>
+        </is>
+      </c>
+      <c r="AE3" s="1" t="inlineStr">
+        <is>
           <t>Displacement</t>
         </is>
       </c>
-      <c r="AA3" s="1" t="inlineStr">
+      <c r="AF3" s="1" t="inlineStr">
         <is>
           <t>MedianSpeed</t>
         </is>
       </c>
-      <c r="AB3" s="1" t="inlineStr">
+      <c r="AG3" s="1" t="inlineStr">
         <is>
           <t>MedianAcceleration</t>
         </is>
       </c>
-      <c r="AC3" s="1" t="inlineStr">
+      <c r="AH3" s="1" t="inlineStr">
         <is>
           <t>FreezingTime</t>
         </is>
       </c>
-      <c r="AD3" s="1" t="inlineStr">
+      <c r="AI3" s="1" t="inlineStr">
         <is>
           <t>Entries</t>
         </is>
       </c>
-      <c r="AE3" s="1" t="inlineStr">
+      <c r="AJ3" s="1" t="inlineStr">
         <is>
           <t>SecondsPresent</t>
         </is>
       </c>
-      <c r="AF3" s="1" t="inlineStr">
+      <c r="AK3" s="1" t="inlineStr">
         <is>
           <t>Displacement</t>
         </is>
       </c>
-      <c r="AG3" s="1" t="inlineStr">
+      <c r="AL3" s="1" t="inlineStr">
         <is>
           <t>MedianSpeed</t>
         </is>
       </c>
-      <c r="AH3" s="1" t="inlineStr">
+      <c r="AM3" s="1" t="inlineStr">
         <is>
           <t>MedianAcceleration</t>
         </is>
       </c>
-      <c r="AI3" s="1" t="inlineStr">
+      <c r="AN3" s="1" t="inlineStr">
         <is>
           <t>FreezingTime</t>
         </is>
       </c>
-      <c r="AJ3" s="1" t="inlineStr">
+      <c r="AO3" s="1" t="inlineStr">
         <is>
           <t>Entries</t>
         </is>
       </c>
-      <c r="AK3" s="1" t="inlineStr">
+      <c r="AP3" s="1" t="inlineStr">
         <is>
           <t>SecondsPresent</t>
         </is>
       </c>
-      <c r="AL3" s="1" t="inlineStr">
+      <c r="AQ3" s="1" t="inlineStr">
         <is>
           <t>Displacement</t>
         </is>
       </c>
-      <c r="AM3" s="1" t="inlineStr">
+      <c r="AR3" s="1" t="inlineStr">
         <is>
           <t>MedianSpeed</t>
         </is>
       </c>
-      <c r="AN3" s="1" t="inlineStr">
+      <c r="AS3" s="1" t="inlineStr">
         <is>
           <t>MedianAcceleration</t>
         </is>
       </c>
-      <c r="AO3" s="1" t="inlineStr">
+      <c r="AT3" s="1" t="inlineStr">
         <is>
           <t>FreezingTime</t>
         </is>
       </c>
-      <c r="AP3" s="1" t="inlineStr">
+      <c r="AU3" s="1" t="inlineStr">
         <is>
           <t>Entries</t>
         </is>
       </c>
-      <c r="AQ3" s="1" t="inlineStr">
+      <c r="AV3" s="1" t="inlineStr">
         <is>
           <t>SecondsPresent</t>
         </is>
       </c>
-      <c r="AR3" s="1" t="inlineStr">
+      <c r="AW3" s="1" t="inlineStr">
         <is>
           <t>Displacement</t>
         </is>
       </c>
-      <c r="AS3" s="1" t="inlineStr">
+      <c r="AX3" s="1" t="inlineStr">
         <is>
           <t>MedianSpeed</t>
         </is>
       </c>
-      <c r="AT3" s="1" t="inlineStr">
+      <c r="AY3" s="1" t="inlineStr">
         <is>
           <t>MedianAcceleration</t>
         </is>
       </c>
-      <c r="AU3" s="1" t="inlineStr">
+      <c r="AZ3" s="1" t="inlineStr">
         <is>
           <t>FreezingTime</t>
         </is>
       </c>
-      <c r="AV3" s="1" t="inlineStr">
+      <c r="BA3" s="1" t="inlineStr">
+        <is>
+          <t>Displacement</t>
+        </is>
+      </c>
+      <c r="BB3" s="1" t="inlineStr">
+        <is>
+          <t>MedianSpeed</t>
+        </is>
+      </c>
+      <c r="BC3" s="1" t="inlineStr">
+        <is>
+          <t>MedianAcceleration</t>
+        </is>
+      </c>
+      <c r="BD3" s="1" t="inlineStr">
+        <is>
+          <t>FreezingTime</t>
+        </is>
+      </c>
+      <c r="BE3" s="1" t="inlineStr">
         <is>
           <t>Entries</t>
         </is>
       </c>
-      <c r="AW3" s="1" t="inlineStr">
+      <c r="BF3" s="1" t="inlineStr">
         <is>
           <t>SecondsPresent</t>
         </is>
       </c>
-      <c r="AX3" s="1" t="inlineStr">
+      <c r="BG3" s="1" t="inlineStr">
         <is>
           <t>Displacement</t>
         </is>
       </c>
-      <c r="AY3" s="1" t="inlineStr">
+      <c r="BH3" s="1" t="inlineStr">
         <is>
           <t>MedianSpeed</t>
         </is>
       </c>
-      <c r="AZ3" s="1" t="inlineStr">
+      <c r="BI3" s="1" t="inlineStr">
         <is>
           <t>MedianAcceleration</t>
         </is>
       </c>
-      <c r="BA3" s="1" t="inlineStr">
+      <c r="BJ3" s="1" t="inlineStr">
         <is>
           <t>FreezingTime</t>
         </is>
       </c>
-      <c r="BB3" s="1" t="inlineStr">
-        <is>
-          <t>CenterToPeriphery</t>
-        </is>
-      </c>
-      <c r="BC3" s="1" t="inlineStr">
+      <c r="BK3" s="1" t="inlineStr">
+        <is>
+          <t>Entries</t>
+        </is>
+      </c>
+      <c r="BL3" s="1" t="inlineStr">
+        <is>
+          <t>SecondsPresent</t>
+        </is>
+      </c>
+      <c r="BM3" s="1" t="inlineStr">
         <is>
           <t>Displacement</t>
         </is>
       </c>
-      <c r="BD3" s="1" t="inlineStr">
+      <c r="BN3" s="1" t="inlineStr">
         <is>
           <t>MedianSpeed</t>
         </is>
       </c>
-      <c r="BE3" s="1" t="inlineStr">
+      <c r="BO3" s="1" t="inlineStr">
         <is>
           <t>MedianAcceleration</t>
         </is>
       </c>
-      <c r="BF3" s="1" t="inlineStr">
+      <c r="BP3" s="1" t="inlineStr">
         <is>
           <t>FreezingTime</t>
         </is>
       </c>
-      <c r="BG3" s="1" t="inlineStr">
+      <c r="BQ3" s="1" t="inlineStr">
         <is>
           <t>Entries</t>
         </is>
       </c>
-      <c r="BH3" s="1" t="inlineStr">
+      <c r="BR3" s="1" t="inlineStr">
         <is>
           <t>SecondsPresent</t>
         </is>
       </c>
-      <c r="BI3" s="1" t="inlineStr">
+      <c r="BS3" s="1" t="inlineStr">
         <is>
           <t>Displacement</t>
         </is>
       </c>
-      <c r="BJ3" s="1" t="inlineStr">
+      <c r="BT3" s="1" t="inlineStr">
         <is>
           <t>MedianSpeed</t>
         </is>
       </c>
-      <c r="BK3" s="1" t="inlineStr">
+      <c r="BU3" s="1" t="inlineStr">
         <is>
           <t>MedianAcceleration</t>
         </is>
       </c>
-      <c r="BL3" s="1" t="inlineStr">
+      <c r="BV3" s="1" t="inlineStr">
         <is>
           <t>FreezingTime</t>
         </is>
       </c>
-      <c r="BM3" s="1" t="inlineStr">
+      <c r="BW3" s="1" t="inlineStr">
         <is>
           <t>Entries</t>
         </is>
       </c>
-      <c r="BN3" s="1" t="inlineStr">
+      <c r="BX3" s="1" t="inlineStr">
         <is>
           <t>SecondsPresent</t>
         </is>
       </c>
-      <c r="BO3" s="1" t="inlineStr">
+      <c r="BY3" s="1" t="inlineStr">
         <is>
           <t>Displacement</t>
         </is>
       </c>
-      <c r="BP3" s="1" t="inlineStr">
+      <c r="BZ3" s="1" t="inlineStr">
         <is>
           <t>MedianSpeed</t>
         </is>
       </c>
-      <c r="BQ3" s="1" t="inlineStr">
+      <c r="CA3" s="1" t="inlineStr">
         <is>
           <t>MedianAcceleration</t>
         </is>
       </c>
-      <c r="BR3" s="1" t="inlineStr">
+      <c r="CB3" s="1" t="inlineStr">
         <is>
           <t>FreezingTime</t>
         </is>
       </c>
-      <c r="BS3" s="1" t="inlineStr">
+      <c r="CC3" s="1" t="inlineStr">
+        <is>
+          <t>Displacement</t>
+        </is>
+      </c>
+      <c r="CD3" s="1" t="inlineStr">
+        <is>
+          <t>MedianSpeed</t>
+        </is>
+      </c>
+      <c r="CE3" s="1" t="inlineStr">
+        <is>
+          <t>MedianAcceleration</t>
+        </is>
+      </c>
+      <c r="CF3" s="1" t="inlineStr">
+        <is>
+          <t>FreezingTime</t>
+        </is>
+      </c>
+      <c r="CG3" s="1" t="inlineStr">
         <is>
           <t>Entries</t>
         </is>
       </c>
-      <c r="BT3" s="1" t="inlineStr">
+      <c r="CH3" s="1" t="inlineStr">
         <is>
           <t>SecondsPresent</t>
         </is>
       </c>
-      <c r="BU3" s="1" t="inlineStr">
+      <c r="CI3" s="1" t="inlineStr">
         <is>
           <t>Displacement</t>
         </is>
       </c>
-      <c r="BV3" s="1" t="inlineStr">
+      <c r="CJ3" s="1" t="inlineStr">
         <is>
           <t>MedianSpeed</t>
         </is>
       </c>
-      <c r="BW3" s="1" t="inlineStr">
+      <c r="CK3" s="1" t="inlineStr">
         <is>
           <t>MedianAcceleration</t>
         </is>
       </c>
-      <c r="BX3" s="1" t="inlineStr">
+      <c r="CL3" s="1" t="inlineStr">
         <is>
           <t>FreezingTime</t>
         </is>
       </c>
-      <c r="BY3" s="1" t="inlineStr">
+      <c r="CM3" s="1" t="inlineStr">
         <is>
           <t>Entries</t>
         </is>
       </c>
-      <c r="BZ3" s="1" t="inlineStr">
+      <c r="CN3" s="1" t="inlineStr">
         <is>
           <t>SecondsPresent</t>
         </is>
       </c>
-      <c r="CA3" s="1" t="inlineStr">
+      <c r="CO3" s="1" t="inlineStr">
         <is>
           <t>Displacement</t>
         </is>
       </c>
-      <c r="CB3" s="1" t="inlineStr">
+      <c r="CP3" s="1" t="inlineStr">
         <is>
           <t>MedianSpeed</t>
         </is>
       </c>
-      <c r="CC3" s="1" t="inlineStr">
+      <c r="CQ3" s="1" t="inlineStr">
         <is>
           <t>MedianAcceleration</t>
         </is>
       </c>
-      <c r="CD3" s="1" t="inlineStr">
+      <c r="CR3" s="1" t="inlineStr">
         <is>
           <t>FreezingTime</t>
         </is>
       </c>
-      <c r="CE3" s="1" t="inlineStr">
-        <is>
-          <t>CenterToPeriphery</t>
-        </is>
-      </c>
-      <c r="CF3" s="1" t="inlineStr">
+      <c r="CS3" s="1" t="inlineStr">
+        <is>
+          <t>Entries</t>
+        </is>
+      </c>
+      <c r="CT3" s="1" t="inlineStr">
+        <is>
+          <t>SecondsPresent</t>
+        </is>
+      </c>
+      <c r="CU3" s="1" t="inlineStr">
         <is>
           <t>Displacement</t>
         </is>
       </c>
-      <c r="CG3" s="1" t="inlineStr">
+      <c r="CV3" s="1" t="inlineStr">
         <is>
           <t>MedianSpeed</t>
         </is>
       </c>
-      <c r="CH3" s="1" t="inlineStr">
+      <c r="CW3" s="1" t="inlineStr">
         <is>
           <t>MedianAcceleration</t>
         </is>
       </c>
-      <c r="CI3" s="1" t="inlineStr">
+      <c r="CX3" s="1" t="inlineStr">
         <is>
           <t>FreezingTime</t>
         </is>
       </c>
-      <c r="CJ3" s="1" t="inlineStr">
+      <c r="CY3" s="1" t="inlineStr">
         <is>
           <t>Entries</t>
         </is>
       </c>
-      <c r="CK3" s="1" t="inlineStr">
-        <is>
-          <t>SecondsPresent</t>
-        </is>
-      </c>
-      <c r="CL3" s="1" t="inlineStr">
-        <is>
-          <t>Displacement</t>
-        </is>
-      </c>
-      <c r="CM3" s="1" t="inlineStr">
-        <is>
-          <t>MedianSpeed</t>
-        </is>
-      </c>
-      <c r="CN3" s="1" t="inlineStr">
-        <is>
-          <t>MedianAcceleration</t>
-        </is>
-      </c>
-      <c r="CO3" s="1" t="inlineStr">
-        <is>
-          <t>FreezingTime</t>
-        </is>
-      </c>
-      <c r="CP3" s="1" t="inlineStr">
-        <is>
-          <t>Entries</t>
-        </is>
-      </c>
-      <c r="CQ3" s="1" t="inlineStr">
-        <is>
-          <t>SecondsPresent</t>
-        </is>
-      </c>
-      <c r="CR3" s="1" t="inlineStr">
-        <is>
-          <t>Displacement</t>
-        </is>
-      </c>
-      <c r="CS3" s="1" t="inlineStr">
-        <is>
-          <t>MedianSpeed</t>
-        </is>
-      </c>
-      <c r="CT3" s="1" t="inlineStr">
-        <is>
-          <t>MedianAcceleration</t>
-        </is>
-      </c>
-      <c r="CU3" s="1" t="inlineStr">
-        <is>
-          <t>FreezingTime</t>
-        </is>
-      </c>
-      <c r="CV3" s="1" t="inlineStr">
-        <is>
-          <t>Entries</t>
-        </is>
-      </c>
-      <c r="CW3" s="1" t="inlineStr">
-        <is>
-          <t>SecondsPresent</t>
-        </is>
-      </c>
-      <c r="CX3" s="1" t="inlineStr">
-        <is>
-          <t>Displacement</t>
-        </is>
-      </c>
-      <c r="CY3" s="1" t="inlineStr">
-        <is>
-          <t>MedianSpeed</t>
-        </is>
-      </c>
       <c r="CZ3" s="1" t="inlineStr">
-        <is>
-          <t>MedianAcceleration</t>
-        </is>
-      </c>
-      <c r="DA3" s="1" t="inlineStr">
-        <is>
-          <t>FreezingTime</t>
-        </is>
-      </c>
-      <c r="DB3" s="1" t="inlineStr">
-        <is>
-          <t>Entries</t>
-        </is>
-      </c>
-      <c r="DC3" s="1" t="inlineStr">
         <is>
           <t>SecondsPresent</t>
         </is>
@@ -1333,10 +1300,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="A5" s="1" t="n">
+        <v>160</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
@@ -1411,269 +1376,258 @@
         <v>26.90399404506588</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01688417470470649</v>
+        <v>0.01689950483264424</v>
       </c>
       <c r="W5" t="n">
-        <v>0.008320383402630194</v>
+        <v>0.008311274447794448</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>215.7333333333333</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.9831272261667467</v>
+        <v>19.78775884225693</v>
       </c>
       <c r="Z5" t="n">
-        <v>26.61927570382476</v>
+        <v>0.0199796122850484</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01718603256541362</v>
+        <v>0.01032707021836463</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.008460069574047657</v>
+        <v>144.9333333333333</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AD5" t="n">
+        <v>219.7</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>11.38836530154244</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.03082692844344273</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.01683361416718835</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>12.96273058377602</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.01453246040001798</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.008484033264712075</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>151.7666666666667</v>
+      </c>
+      <c r="AO5" t="n">
         <v>22</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AP5" t="n">
         <v>497.3666666666667</v>
       </c>
-      <c r="AF5" t="n">
-        <v>25.21284800736521</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0.01916763944294997</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0.009316622688565479</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
+      <c r="AQ5" t="n">
+        <v>14.98191584527509</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.01644875547449016</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0.008169733486451764</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>140</v>
+      </c>
+      <c r="AU5" t="n">
         <v>16</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AV5" t="n">
         <v>92.43333333333334</v>
       </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>6.674586104010562</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.674586104010562</v>
+        <v>0.009015418389323737</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.008890308792222745</v>
+        <v>0.004402332297612999</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.004347444658280963</v>
+        <v>105.7</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>2.344916407180044</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.9796062344173422</v>
+        <v>0.007590843744853823</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.412854777268132</v>
+        <v>0.004311367872632151</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.008982540069311429</v>
+        <v>69.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.004428353109649175</v>
+        <v>4</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>209.8333333333333</v>
       </c>
       <c r="BG5" t="n">
+        <v>0.5314246081946006</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0.03455052996016539</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0.02067664294747129</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>3.574723261565454</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0.01386683173948229</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0.009306549994134779</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>41</v>
+      </c>
+      <c r="BQ5" t="n">
         <v>6</v>
       </c>
-      <c r="BH5" t="n">
+      <c r="BR5" t="n">
         <v>30.23333333333333</v>
       </c>
-      <c r="BI5" t="n">
-        <v>3.169511133790516</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0.01271001255041576</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0.006356121021903305</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM5" t="n">
+      <c r="BS5" t="n">
+        <v>0.5477506617087389</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0.05691416114116655</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0.01870509188483838</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW5" t="n">
         <v>3</v>
       </c>
-      <c r="BN5" t="n">
+      <c r="BX5" t="n">
         <v>13.93333333333333</v>
       </c>
-      <c r="BO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>0</v>
-      </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>5.893042800688687</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>0.006980556536495985</v>
       </c>
       <c r="CA5" t="n">
-        <v>5.893042800688687</v>
+        <v>0.003728269819896379</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.006967181143240853</v>
+        <v>137.4</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.003728269819896379</v>
+        <v>1.823770997057423</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>0.00759351644797867</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.9756100200869539</v>
+        <v>0.003130196056339864</v>
       </c>
       <c r="CF5" t="n">
-        <v>4.015778625357701</v>
+        <v>87.86666666666667</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.007022761692770274</v>
+        <v>3</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.003336069199297409</v>
+        <v>229.3333333333333</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>0.6762260992319052</v>
       </c>
       <c r="CJ5" t="n">
+        <v>0.03967215100802779</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.03230919827504553</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS5" t="n">
         <v>2</v>
       </c>
-      <c r="CK5" t="n">
+      <c r="CT5" t="n">
         <v>19.13333333333333</v>
       </c>
-      <c r="CL5" t="n">
-        <v>4.02916638745015</v>
-      </c>
-      <c r="CM5" t="n">
-        <v>0.00732098920037616</v>
-      </c>
-      <c r="CN5" t="n">
-        <v>0.003889595796696232</v>
-      </c>
-      <c r="CO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP5" t="n">
+      <c r="CU5" t="n">
+        <v>0.5056875670809948</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0.01137372606766152</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>0.00384150893416213</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="CY5" t="n">
         <v>3</v>
       </c>
-      <c r="CQ5" t="n">
+      <c r="CZ5" t="n">
         <v>28.13333333333333</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
+      <c r="A6" s="1" t="n">
+        <v>161</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
@@ -1754,263 +1708,252 @@
         <v>0.01788550011389833</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>115.6333333333333</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.9815487683869147</v>
+        <v>24.03478507455025</v>
       </c>
       <c r="Z6" t="n">
-        <v>43.88837745363931</v>
+        <v>0.0337285199392111</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03560734169308721</v>
+        <v>0.01944224715645267</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01831380782748504</v>
+        <v>78.43333333333334</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AD6" t="n">
+        <v>418.9333333333333</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>18.8429579737902</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.04208116358306516</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.02483509288599153</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>233.9666666666667</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>23.44990686346938</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.03747115330335485</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.02113248830858851</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>55.59999999999999</v>
+      </c>
+      <c r="AO6" t="n">
         <v>33</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AP6" t="n">
         <v>110.3666666666667</v>
       </c>
-      <c r="AF6" t="n">
-        <v>43.57221584681332</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.03558755220535725</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.01829593041428973</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
+      <c r="AQ6" t="n">
+        <v>16.28604452424785</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.04644627485062254</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.02458648003539899</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>21.46666666666667</v>
+      </c>
+      <c r="AU6" t="n">
         <v>24</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AV6" t="n">
         <v>136.7333333333333</v>
       </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>13.66045461141933</v>
       </c>
       <c r="AX6" t="n">
-        <v>13.66045461141933</v>
+        <v>0.02763936397885053</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.02763936397885053</v>
+        <v>0.01196546215456684</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.01196546215456684</v>
+        <v>50.03333333333333</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>5.407706614545068</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.9777988107395293</v>
+        <v>0.01910524178351855</v>
       </c>
       <c r="BC6" t="n">
-        <v>13.1404177140825</v>
+        <v>0.01108285176505275</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.02467788712934293</v>
+        <v>38.36666666666667</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.01295617294300966</v>
+        <v>9</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>142.8</v>
       </c>
       <c r="BG6" t="n">
+        <v>3.1327689183804</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0.05337379087557433</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0.03533465943533547</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1.033333333333333</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>52</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>4.998268117201207</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0.0327238163531826</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0.02314220362793864</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>13.56666666666667</v>
+      </c>
+      <c r="BQ6" t="n">
         <v>8</v>
       </c>
-      <c r="BH6" t="n">
+      <c r="BR6" t="n">
         <v>67.3</v>
       </c>
-      <c r="BI6" t="n">
-        <v>13.09956386845325</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.02848860378394741</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0.01328604814967305</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM6" t="n">
+      <c r="BS6" t="n">
+        <v>7.845747037048383</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0.03897930197772533</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>0.02041143795087027</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="BW6" t="n">
         <v>7</v>
       </c>
-      <c r="BN6" t="n">
+      <c r="BX6" t="n">
         <v>37.9</v>
       </c>
-      <c r="BO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>0</v>
-      </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>9.632661380812261</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>0.011707981671226</v>
       </c>
       <c r="CA6" t="n">
-        <v>9.632661380812261</v>
+        <v>0.005399918704994011</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.011707981671226</v>
+        <v>79.53333333333333</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.005399918704994011</v>
+        <v>4.993492357943044</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>0.01799832594307021</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.9690580181447509</v>
+        <v>0.007871877586363941</v>
       </c>
       <c r="CF6" t="n">
-        <v>7.830610025836286</v>
+        <v>44.76666666666667</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.01083126027044634</v>
+        <v>6</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.006026602171586681</v>
+        <v>46.3</v>
       </c>
       <c r="CI6" t="n">
-        <v>0</v>
+        <v>4.412221940822535</v>
       </c>
       <c r="CJ6" t="n">
+        <v>0.02001204206634036</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.01001271742771728</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>26.53333333333333</v>
+      </c>
+      <c r="CM6" t="n">
         <v>6</v>
       </c>
-      <c r="CK6" t="n">
+      <c r="CN6" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>1.688456846555143</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0.03834304368340646</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0.02496783470206028</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>6</v>
+      </c>
+      <c r="CT6" t="n">
         <v>26.96666666666667</v>
       </c>
-      <c r="CL6" t="n">
-        <v>8.37539275935816</v>
-      </c>
-      <c r="CM6" t="n">
-        <v>0.01185590304481354</v>
-      </c>
-      <c r="CN6" t="n">
-        <v>0.005047219888627108</v>
-      </c>
-      <c r="CO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP6" t="n">
+      <c r="CU6" t="n">
+        <v>2.766860399715838</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0.02707348257951745</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>0.01016116502487718</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>24.56666666666667</v>
+      </c>
+      <c r="CY6" t="n">
         <v>4</v>
       </c>
-      <c r="CQ6" t="n">
+      <c r="CZ6" t="n">
         <v>113.9333333333333</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
+      <c r="A7" s="1" t="n">
+        <v>162</v>
       </c>
       <c r="B7" t="n">
         <v>2</v>
@@ -2091,263 +2034,252 @@
         <v>0.008772869642120873</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>164.3666666666667</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.9797492815405076</v>
+        <v>19.29535841669631</v>
       </c>
       <c r="Z7" t="n">
-        <v>28.82652313178765</v>
+        <v>0.01649142823602317</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0184299586320098</v>
+        <v>0.00943514879020377</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.008900610764080552</v>
+        <v>141.1666666666667</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AD7" t="n">
+        <v>449.5666666666667</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>11.90223781407098</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.02420388637150227</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.01322484350896739</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>55.50000000000001</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>90.06666666666666</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>13.63308102562672</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.02495505725894327</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.01334848049745594</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>53.96666666666667</v>
+      </c>
+      <c r="AO7" t="n">
         <v>28</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AP7" t="n">
         <v>228.9333333333333</v>
       </c>
-      <c r="AF7" t="n">
-        <v>30.76353949728617</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0.01815482283367109</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0.009015411246677596</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
+      <c r="AQ7" t="n">
+        <v>17.91887467077758</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.01878909178685742</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.009677918931183065</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>98.33333333333334</v>
+      </c>
+      <c r="AU7" t="n">
         <v>18</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AV7" t="n">
         <v>124.8666666666667</v>
       </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>10.24403968454883</v>
       </c>
       <c r="AX7" t="n">
-        <v>10.24403968454883</v>
+        <v>0.01652710337915675</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.0168356243054596</v>
+        <v>0.006883802727593813</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.006972706660508754</v>
+        <v>74.86666666666666</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>4.999250578642261</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.9717259565788646</v>
+        <v>0.02749996016736586</v>
       </c>
       <c r="BC7" t="n">
-        <v>9.139884144214575</v>
+        <v>0.01481298623786085</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.02928224015676806</v>
+        <v>15.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.01277093683986297</v>
+        <v>5</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>38.7</v>
       </c>
       <c r="BG7" t="n">
+        <v>2.561107867639759</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0.01981645353890424</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0.01351507703122017</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>45.06666666666667</v>
+      </c>
+      <c r="BK7" t="n">
         <v>7</v>
       </c>
-      <c r="BH7" t="n">
+      <c r="BL7" t="n">
+        <v>117.2333333333333</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.859459017711014</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0.02982896880114308</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0.02359349101541002</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR7" t="n">
         <v>53.5</v>
       </c>
-      <c r="BI7" t="n">
-        <v>9.353346581537515</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.03147628460048335</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.0177417272955791</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM7" t="n">
+      <c r="BS7" t="n">
+        <v>3.206726027175115</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0.02314188814167546</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0.01358771905969787</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>9.933333333333334</v>
+      </c>
+      <c r="BW7" t="n">
         <v>8</v>
       </c>
-      <c r="BN7" t="n">
+      <c r="BX7" t="n">
         <v>90.56666666666666</v>
       </c>
-      <c r="BO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>0</v>
-      </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>7.482305966895996</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>0.0096765747387485</v>
       </c>
       <c r="CA7" t="n">
-        <v>7.482305966895996</v>
+        <v>0.006620142445227017</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.009661197901630891</v>
+        <v>92.46666666666667</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.006620142445227017</v>
+        <v>0.4949493563325409</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>0.01187117060773862</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.9742435929738553</v>
+        <v>0.006493900671665331</v>
       </c>
       <c r="CF7" t="n">
-        <v>6.785437873812334</v>
+        <v>4.366666666666666</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.009337530590480703</v>
+        <v>2</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.006330259876609956</v>
+        <v>25.53333333333333</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>0.4203277904421319</v>
       </c>
       <c r="CJ7" t="n">
+        <v>0.06101356339837816</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.01861656071801077</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>16.23333333333333</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>1.23413307650236</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0.01027388343028452</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0.005400156924366278</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>18.73333333333333</v>
+      </c>
+      <c r="CS7" t="n">
         <v>3</v>
       </c>
-      <c r="CK7" t="n">
+      <c r="CT7" t="n">
         <v>139.4</v>
       </c>
-      <c r="CL7" t="n">
-        <v>5.939209267541438</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>0.01015550610207883</v>
-      </c>
-      <c r="CN7" t="n">
-        <v>0.006625752939608542</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP7" t="n">
+      <c r="CU7" t="n">
+        <v>2.339036138249497</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0.01408682096204858</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>0.008783182959086831</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="CY7" t="n">
         <v>5</v>
       </c>
-      <c r="CQ7" t="n">
+      <c r="CZ7" t="n">
         <v>118.8333333333333</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
+      <c r="A8" s="1" t="n">
+        <v>163</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
@@ -2425,266 +2357,255 @@
         <v>0.03150482332033933</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01771946614491082</v>
+        <v>0.01765171579288893</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>83.16666666666667</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.97559281612913</v>
+        <v>17.94511197433813</v>
       </c>
       <c r="Z8" t="n">
-        <v>38.49894229843743</v>
+        <v>0.04344771788363395</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03459429464709535</v>
+        <v>0.02637045704101186</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.02021871385607943</v>
+        <v>15.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AD8" t="n">
+        <v>132.7666666666667</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>23.91842905808523</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.03411224666109877</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.0205258591516644</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>431.8333333333333</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>19.07097188038509</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.03697451039702958</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.02270110314767109</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>34.56666666666667</v>
+      </c>
+      <c r="AO8" t="n">
         <v>24</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AP8" t="n">
         <v>89.73333333333333</v>
       </c>
-      <c r="AF8" t="n">
-        <v>41.50847981701492</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.03120333341563658</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.01816854459797268</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
+      <c r="AQ8" t="n">
+        <v>23.97999888998891</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.0413338900987825</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.02550069378961129</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>31.86666666666667</v>
+      </c>
+      <c r="AU8" t="n">
         <v>38</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AV8" t="n">
         <v>224.0333333333333</v>
       </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>9.839768003264494</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.839768003264494</v>
+        <v>0.0155915884280442</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.0155915884280442</v>
+        <v>0.00762972402610651</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.00762972402610651</v>
+        <v>48.46666666666667</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>2.673517981724629</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.96987874962474</v>
+        <v>0.04077593260417222</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.356357494258537</v>
+        <v>0.02289838803044385</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0175585365669042</v>
+        <v>3.533333333333333</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.009078783144069846</v>
+        <v>7</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>26.23333333333333</v>
       </c>
       <c r="BG8" t="n">
+        <v>3.172325144387177</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0.04237200579534819</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0.02101016823866551</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>3.533333333333333</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>47.56666666666667</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.9557592032387802</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0.02284053675714048</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0.01711557216388471</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BQ8" t="n">
         <v>5</v>
       </c>
-      <c r="BH8" t="n">
+      <c r="BR8" t="n">
         <v>36.46666666666667</v>
       </c>
-      <c r="BI8" t="n">
-        <v>9.287597174744064</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.01537302418401232</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.007575332844516502</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM8" t="n">
+      <c r="BS8" t="n">
+        <v>3.999538836757428</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0.0172772552786232</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0.00795340701113253</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>34.03333333333333</v>
+      </c>
+      <c r="BW8" t="n">
         <v>7</v>
       </c>
-      <c r="BN8" t="n">
+      <c r="BX8" t="n">
         <v>189.7333333333333</v>
       </c>
-      <c r="BO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>0</v>
-      </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>7.287779512074638</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>0.009284821234387897</v>
       </c>
       <c r="CA8" t="n">
-        <v>7.287779512074638</v>
+        <v>0.004261874486034989</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.009364694155864051</v>
+        <v>102.3333333333333</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.004285327748240864</v>
+        <v>0.3641455067177531</v>
       </c>
       <c r="CD8" t="n">
-        <v>0</v>
+        <v>0.01979060813829414</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.9652959144521606</v>
+        <v>0.06917001344050966</v>
       </c>
       <c r="CF8" t="n">
-        <v>5.555946194623343</v>
+        <v>0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.01196188523223829</v>
+        <v>3</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.007395681457049275</v>
+        <v>17.6</v>
       </c>
       <c r="CI8" t="n">
-        <v>0</v>
+        <v>2.034015224996198</v>
       </c>
       <c r="CJ8" t="n">
+        <v>0.009701081525158082</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0.003205386406846273</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>60.36666666666667</v>
+      </c>
+      <c r="CM8" t="n">
         <v>3</v>
       </c>
-      <c r="CK8" t="n">
+      <c r="CN8" t="n">
+        <v>128.2</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0.2477406984106381</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0.040460566585516</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>0.01421118152517353</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>1.066666666666667</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>3</v>
+      </c>
+      <c r="CT8" t="n">
         <v>20.1</v>
       </c>
-      <c r="CL8" t="n">
-        <v>6.649164240383389</v>
-      </c>
-      <c r="CM8" t="n">
-        <v>0.01232390510494241</v>
-      </c>
-      <c r="CN8" t="n">
-        <v>0.007320752411933196</v>
-      </c>
-      <c r="CO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP8" t="n">
+      <c r="CU8" t="n">
+        <v>1.730707124390356</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0.01078977251789403</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0.006249896535882896</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>32</v>
+      </c>
+      <c r="CY8" t="n">
         <v>5</v>
       </c>
-      <c r="CQ8" t="n">
+      <c r="CZ8" t="n">
         <v>134.1</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC8" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="A9" s="1" t="n">
+        <v>116</v>
       </c>
       <c r="B9" t="n">
         <v>3</v>
@@ -2759,269 +2680,258 @@
         <v>43.07787042967787</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03606882175914083</v>
+        <v>0.03611108575061128</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02055816578539904</v>
+        <v>0.02061835806961398</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>95.66666666666667</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.9820004898358786</v>
+        <v>20.10426124507164</v>
       </c>
       <c r="Z9" t="n">
-        <v>42.81279999025273</v>
+        <v>0.03497492463286933</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03592379195248285</v>
+        <v>0.022423338530675</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.02055816578539904</v>
+        <v>54.53333333333333</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AD9" t="n">
+        <v>405.8333333333333</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>18.16157265701086</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.0438541216922359</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.02672671763534832</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>23.63333333333333</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>31</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>201.5333333333333</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>23.4231597942284</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.03679292029731169</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.01915303827467138</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>47.03333333333333</v>
+      </c>
+      <c r="AO9" t="n">
         <v>29</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AP9" t="n">
         <v>142.8666666666667</v>
       </c>
-      <c r="AF9" t="n">
-        <v>42.04360023516361</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.03600572809096447</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.02063192546478809</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
+      <c r="AQ9" t="n">
+        <v>18.75327541986555</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.04345789476494766</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.0243489131477588</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>20.93333333333334</v>
+      </c>
+      <c r="AU9" t="n">
         <v>19</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AV9" t="n">
         <v>149.7666666666667</v>
       </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>9.12448975377065</v>
       </c>
       <c r="AX9" t="n">
-        <v>9.12448975377065</v>
+        <v>0.01575659100671223</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.01575659100671223</v>
+        <v>0.009855082943372007</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.009855082943372007</v>
+        <v>67.83333333333333</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>0.4752338369656623</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.9755267667247959</v>
+        <v>0.04619355852847917</v>
       </c>
       <c r="BC9" t="n">
-        <v>8.541639418813553</v>
+        <v>0.0372982878212223</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.01780055746276932</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.008046154148504958</v>
+        <v>2</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="BG9" t="n">
+        <v>3.022998111635634</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0.05341546551661122</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0.03426795202838832</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>2.841596940647876</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0.01397114177007554</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.006019869925514001</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>41.03333333333333</v>
+      </c>
+      <c r="BQ9" t="n">
         <v>8</v>
       </c>
-      <c r="BH9" t="n">
+      <c r="BR9" t="n">
         <v>41.23333333333333</v>
       </c>
-      <c r="BI9" t="n">
-        <v>9.12448975377065</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0.01575659100671223</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>0.009855082943372007</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM9" t="n">
+      <c r="BS9" t="n">
+        <v>6.094443961974397</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0.0210400984010574</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0.01017834138257817</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>52.09999999999999</v>
+      </c>
+      <c r="BW9" t="n">
         <v>12</v>
       </c>
-      <c r="BN9" t="n">
+      <c r="BX9" t="n">
         <v>209.2333333333333</v>
       </c>
-      <c r="BO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>0</v>
-      </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>8.04806338236687</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>0.01211128100292402</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.04806338236687</v>
+        <v>0.007229916838111694</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.01211128100292402</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.007229916838111694</v>
+        <v>2.324074482515717</v>
       </c>
       <c r="CD9" t="n">
-        <v>0</v>
+        <v>0.01025593525372823</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.9741027822016657</v>
+        <v>0.006266355223021581</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.284132804758943</v>
+        <v>61.96666666666667</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.01954001060879351</v>
+        <v>6</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.007999683064756402</v>
+        <v>187.9</v>
       </c>
       <c r="CI9" t="n">
-        <v>0</v>
+        <v>1.913586259264488</v>
       </c>
       <c r="CJ9" t="n">
+        <v>0.03740863312912184</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0.02203390084559763</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>5</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>68.43333333333334</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS9" t="n">
         <v>2</v>
       </c>
-      <c r="CK9" t="n">
+      <c r="CT9" t="n">
         <v>14.13333333333333</v>
       </c>
-      <c r="CL9" t="n">
-        <v>4.182526285864395</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>0.02543142407671795</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>0.01138284244203125</v>
-      </c>
-      <c r="CO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP9" t="n">
+      <c r="CU9" t="n">
+        <v>0.6282467811677679</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0.03807266661031958</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>0.01374078884819103</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY9" t="n">
         <v>3</v>
       </c>
-      <c r="CQ9" t="n">
+      <c r="CZ9" t="n">
         <v>29.53333333333333</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC9" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
+      <c r="A10" s="1" t="n">
+        <v>117</v>
       </c>
       <c r="B10" t="n">
         <v>3</v>
@@ -3096,269 +3006,258 @@
         <v>29.97167377438802</v>
       </c>
       <c r="V10" t="n">
-        <v>0.02005535375296286</v>
+        <v>0.02013624264578806</v>
       </c>
       <c r="W10" t="n">
         <v>0.01001169619879838</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>210.4333333333333</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.9848865216140676</v>
+        <v>14.06171529903697</v>
       </c>
       <c r="Z10" t="n">
-        <v>28.34722791942455</v>
+        <v>0.02997851983340469</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.01921616041522523</v>
+        <v>0.02060952485335218</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.009972591424241728</v>
+        <v>55.83333333333333</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AD10" t="n">
+        <v>184.5666666666667</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>7.850778879143147</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.04074295045864313</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.02984512145263249</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>7.966666666666667</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>11.05934042742352</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.0135596670174489</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.007197520590215223</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>198.4</v>
+      </c>
+      <c r="AO10" t="n">
         <v>26</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AP10" t="n">
         <v>533.2333333333333</v>
       </c>
-      <c r="AF10" t="n">
-        <v>27.958169467341</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0.01923212103267302</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0.009922861461201693</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
+      <c r="AQ10" t="n">
+        <v>8.528811644032253</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.02947224043376391</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.01791163707343923</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>48.63333333333334</v>
+      </c>
+      <c r="AU10" t="n">
         <v>18</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AV10" t="n">
         <v>106.5</v>
       </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>7.662465997634749</v>
       </c>
       <c r="AX10" t="n">
-        <v>7.662465997634749</v>
+        <v>0.009499246432415287</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.009499246432415287</v>
+        <v>0.005090835875937616</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.005132103815125855</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>2.563955756481831</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.9751891014750685</v>
+        <v>0.01082463985397642</v>
       </c>
       <c r="BC10" t="n">
-        <v>7.039771839818912</v>
+        <v>0.004688438306911086</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.00932163801808783</v>
+        <v>35.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.004630043500115422</v>
+        <v>4</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>202.1666666666667</v>
       </c>
       <c r="BG10" t="n">
+        <v>0.5329484768272023</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0.05521550472740261</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0.03926362407658579</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>10.66666666666667</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>3.089553303834412</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0.01265487872612299</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0.006560799375500448</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>22.53333333333333</v>
+      </c>
+      <c r="BQ10" t="n">
         <v>6</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BR10" t="n">
         <v>68.26666666666667</v>
       </c>
-      <c r="BI10" t="n">
-        <v>2.571227707564257</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0.01923696309922085</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.007714446230314032</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM10" t="n">
+      <c r="BS10" t="n">
+        <v>0.5345738552136576</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0.03345571677867945</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0.02883439235633763</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW10" t="n">
         <v>3</v>
       </c>
-      <c r="BN10" t="n">
+      <c r="BX10" t="n">
         <v>18.9</v>
       </c>
-      <c r="BO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>0</v>
-      </c>
       <c r="BY10" t="n">
-        <v>0</v>
+        <v>6.314161027991828</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>0.008744228326439174</v>
       </c>
       <c r="CA10" t="n">
-        <v>6.314161027991828</v>
+        <v>0.00381964009543756</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.008661608374792351</v>
+        <v>104.2333333333333</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.003786070235902939</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
         <v>0</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.9755145581497001</v>
+        <v>0</v>
       </c>
       <c r="CF10" t="n">
-        <v>5.774316960073216</v>
+        <v>0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.008472557719958251</v>
+        <v>1</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.003571710935396877</v>
+        <v>15.2</v>
       </c>
       <c r="CI10" t="n">
-        <v>0</v>
+        <v>0.6300369842509062</v>
       </c>
       <c r="CJ10" t="n">
+        <v>0.05649527313658009</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0.02072548298958288</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>4</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>15.23333333333333</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>1.450102125542491</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0.007915822275020894</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>0.002969440593852387</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="CS10" t="n">
         <v>2</v>
       </c>
-      <c r="CK10" t="n">
+      <c r="CT10" t="n">
         <v>182.3</v>
       </c>
-      <c r="CL10" t="n">
-        <v>5.274195201854068</v>
-      </c>
-      <c r="CM10" t="n">
-        <v>0.009885651822812092</v>
-      </c>
-      <c r="CN10" t="n">
-        <v>0.004604886662327945</v>
-      </c>
-      <c r="CO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP10" t="n">
+      <c r="CU10" t="n">
+        <v>3.273102919054945</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0.01993159176414367</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>0.004838090876228187</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>29.83333333333333</v>
+      </c>
+      <c r="CY10" t="n">
         <v>4</v>
       </c>
-      <c r="CQ10" t="n">
+      <c r="CZ10" t="n">
         <v>87.26666666666667</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
+      <c r="A11" s="1" t="n">
+        <v>118</v>
       </c>
       <c r="B11" t="n">
         <v>3</v>
@@ -3433,269 +3332,258 @@
         <v>55.54785797690239</v>
       </c>
       <c r="V11" t="n">
-        <v>0.04994930111679413</v>
+        <v>0.05003728415651104</v>
       </c>
       <c r="W11" t="n">
-        <v>0.02728870137736072</v>
+        <v>0.02738862754346028</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>24.93333333333333</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.9785750557634602</v>
+        <v>29.20606394235837</v>
       </c>
       <c r="Z11" t="n">
-        <v>53.87601641784529</v>
+        <v>0.05492511019961666</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.05194500862001994</v>
+        <v>0.03314009531019207</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.02878074911287465</v>
+        <v>17.03333333333333</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AD11" t="n">
+        <v>301.8</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>23.44475817722014</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.05905012882949722</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.03501682178864312</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>37</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>274.3333333333333</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>26.64122725250443</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.04723465610823011</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.02642213624771315</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="AO11" t="n">
         <v>34</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AP11" t="n">
         <v>137.8</v>
       </c>
-      <c r="AF11" t="n">
-        <v>54.40481206502913</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0.04927832533640797</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.02726179301349352</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
+      <c r="AQ11" t="n">
+        <v>16.12382439672033</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.04939603431264766</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.02581885657599989</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU11" t="n">
         <v>25</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AV11" t="n">
         <v>186.0666666666667</v>
       </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>13.1539299587867</v>
       </c>
       <c r="AX11" t="n">
-        <v>13.1539299587867</v>
+        <v>0.03109226751502703</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.03109226751502703</v>
+        <v>0.01532639370565114</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.01532639370565114</v>
+        <v>18.13333333333333</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>6.73370676936411</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.975594977482185</v>
+        <v>0.03123934452219252</v>
       </c>
       <c r="BC11" t="n">
-        <v>7.056615855970092</v>
+        <v>0.01604006011168588</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.03144361220707914</v>
+        <v>14.66666666666667</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.01928016570417507</v>
+        <v>6</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>81.56666666666666</v>
       </c>
       <c r="BG11" t="n">
+        <v>7.670904072557557</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.03027338315846981</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0.01528280384778903</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>17.06666666666667</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>115.5333333333333</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.670601683994634</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0.05690240060133522</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.02481898763005869</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>2.266666666666667</v>
+      </c>
+      <c r="BQ11" t="n">
         <v>3</v>
       </c>
-      <c r="BH11" t="n">
+      <c r="BR11" t="n">
         <v>13.56666666666667</v>
       </c>
-      <c r="BI11" t="n">
-        <v>10.19099383754438</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.0292565960701765</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.01553515089238494</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM11" t="n">
+      <c r="BS11" t="n">
+        <v>2.408583843316836</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0.02591735518010825</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0.01131406372046457</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="BW11" t="n">
         <v>6</v>
       </c>
-      <c r="BN11" t="n">
+      <c r="BX11" t="n">
         <v>89.33333333333333</v>
       </c>
-      <c r="BO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>0</v>
-      </c>
       <c r="BY11" t="n">
-        <v>0</v>
+        <v>6.953930337638047</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>0.01139898216824164</v>
       </c>
       <c r="CA11" t="n">
-        <v>6.953930337638047</v>
+        <v>0.005844484773127934</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.01137142255040086</v>
+        <v>76.56666666666666</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.005844484773127934</v>
+        <v>1.866897111950335</v>
       </c>
       <c r="CD11" t="n">
-        <v>0</v>
+        <v>0.01187692848829514</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.9709316692943644</v>
+        <v>0.005057509217391703</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.309469151000588</v>
+        <v>28.56666666666667</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.02673012577694234</v>
+        <v>4</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.01191821224792666</v>
+        <v>109.0333333333333</v>
       </c>
       <c r="CI11" t="n">
-        <v>0</v>
+        <v>2.269546559125045</v>
       </c>
       <c r="CJ11" t="n">
+        <v>0.01342497133612629</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0.008535938816156944</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>44.63333333333333</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>123.8333333333333</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS11" t="n">
         <v>1</v>
       </c>
-      <c r="CK11" t="n">
+      <c r="CT11" t="n">
         <v>7.533333333333333</v>
       </c>
-      <c r="CL11" t="n">
-        <v>3.233490005939718</v>
-      </c>
-      <c r="CM11" t="n">
-        <v>0.02323119803214757</v>
-      </c>
-      <c r="CN11" t="n">
-        <v>0.01150108714951037</v>
-      </c>
-      <c r="CO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP11" t="n">
+      <c r="CU11" t="n">
+        <v>0.3887876101878227</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>0.0473051254994743</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>0.01390357477988868</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY11" t="n">
         <v>2</v>
       </c>
-      <c r="CQ11" t="n">
+      <c r="CZ11" t="n">
         <v>59.6</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC11" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
+      <c r="A12" s="1" t="n">
+        <v>119</v>
       </c>
       <c r="B12" t="n">
         <v>3</v>
@@ -3770,152 +3658,152 @@
         <v>28.6244137145262</v>
       </c>
       <c r="V12" t="n">
-        <v>0.02068447839520687</v>
+        <v>0.02072114135176023</v>
       </c>
       <c r="W12" t="n">
-        <v>0.009715492271692217</v>
+        <v>0.009715734255605235</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>169.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.9799147582872039</v>
+        <v>16.58383241295595</v>
       </c>
       <c r="Z12" t="n">
-        <v>26.95220742444394</v>
+        <v>0.01988458248018393</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.02007259057916122</v>
+        <v>0.01047796171686858</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.009751839990225608</v>
+        <v>127.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AD12" t="n">
+        <v>625.2333333333333</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>15.05261279251862</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.02733916245239329</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.01512198208142803</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>54.26666666666667</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>135.7333333333333</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>8.062677945749169</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.01686119691267815</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.007257504299924893</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="AO12" t="n">
         <v>17</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AP12" t="n">
         <v>85.43333333333334</v>
       </c>
-      <c r="AF12" t="n">
-        <v>24.36135063087841</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0.02244961689275882</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0.01220615285016569</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
+      <c r="AQ12" t="n">
+        <v>3.331119459968761</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0.03536734605471527</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0.02482158128884311</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>4.466666666666667</v>
+      </c>
+      <c r="AU12" t="n">
         <v>7</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AV12" t="n">
         <v>53.6</v>
       </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>5.143882952642381</v>
       </c>
       <c r="AX12" t="n">
-        <v>5.143882952642381</v>
+        <v>0.008131827612680553</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.008198647189428143</v>
+        <v>0.004165919611739399</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.004238933924115562</v>
+        <v>119.2333333333333</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>2.920129174316707</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.9738835579480235</v>
+        <v>0.008531539870626709</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.116697697040843</v>
+        <v>0.003648223382168705</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.009720774051269365</v>
+        <v>72.60000000000001</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.006191471243540803</v>
+        <v>7</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>228.1</v>
       </c>
       <c r="BG12" t="n">
+        <v>0.4367578272142745</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0.007063167481966781</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0.003353148293115505</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>14</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>65.76666666666667</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.1677613903181749</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0.03385424825374916</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0.01186154260962302</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ12" t="n">
         <v>3</v>
       </c>
-      <c r="BH12" t="n">
+      <c r="BR12" t="n">
         <v>6.133333333333334</v>
       </c>
-      <c r="BI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>0</v>
-      </c>
       <c r="BS12" t="n">
         <v>0</v>
       </c>
@@ -3935,104 +3823,93 @@
         <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>0</v>
+        <v>6.86154072569769</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>0.008384627476287487</v>
       </c>
       <c r="CA12" t="n">
-        <v>6.86154072569769</v>
+        <v>0.005076257404680984</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.008384627476287487</v>
+        <v>124</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.005076257404680984</v>
+        <v>2.26577758595308</v>
       </c>
       <c r="CD12" t="n">
-        <v>0</v>
+        <v>0.009075946845597841</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.9716737580992334</v>
+        <v>0.005357249558812908</v>
       </c>
       <c r="CF12" t="n">
-        <v>6.150295249915358</v>
+        <v>63.43333333333333</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.009035374908093585</v>
+        <v>4</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.00534169458834699</v>
+        <v>172.2666666666667</v>
       </c>
       <c r="CI12" t="n">
-        <v>0</v>
+        <v>0.6889422158209473</v>
       </c>
       <c r="CJ12" t="n">
+        <v>0.0303584072526587</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0.03173463167825585</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>81.83333333333333</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>0.591611532102273</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>0.01783280715937856</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>0.01481045704450606</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>3.766666666666667</v>
+      </c>
+      <c r="CS12" t="n">
         <v>3</v>
       </c>
-      <c r="CK12" t="n">
+      <c r="CT12" t="n">
         <v>26.96666666666667</v>
       </c>
-      <c r="CL12" t="n">
-        <v>5.979282830247277</v>
-      </c>
-      <c r="CM12" t="n">
-        <v>0.00890263260279256</v>
-      </c>
-      <c r="CN12" t="n">
-        <v>0.005241311330449916</v>
-      </c>
-      <c r="CO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP12" t="n">
+      <c r="CU12" t="n">
+        <v>0.6511609625023631</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>0.03620373308523555</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>0.02488285752189347</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>1.033333333333333</v>
+      </c>
+      <c r="CY12" t="n">
         <v>2</v>
       </c>
-      <c r="CQ12" t="n">
+      <c r="CZ12" t="n">
         <v>18.93333333333333</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
+      <c r="A13" s="1" t="n">
+        <v>120</v>
       </c>
       <c r="B13" t="n">
         <v>3</v>
@@ -4107,269 +3984,258 @@
         <v>54.71351962887316</v>
       </c>
       <c r="V13" t="n">
-        <v>0.04871525459786141</v>
+        <v>0.04905838986793082</v>
       </c>
       <c r="W13" t="n">
-        <v>0.02890362117481848</v>
+        <v>0.02889587813428085</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>18.56666666666667</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.9789005922811997</v>
+        <v>26.99763481615011</v>
       </c>
       <c r="Z13" t="n">
-        <v>51.14600995784692</v>
+        <v>0.05103414614411851</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.04811132892977488</v>
+        <v>0.02921317220273281</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.02781630659589085</v>
+        <v>6.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AD13" t="n">
+        <v>245.5666666666667</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>26.1895743518102</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.05499510797059241</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.03264655999913954</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>7.666666666666667</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>37</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>225.1333333333333</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>18.95274625092829</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.04687521123227296</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.02629533148139155</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>6.433333333333334</v>
+      </c>
+      <c r="AO13" t="n">
         <v>36</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AP13" t="n">
         <v>199.7666666666667</v>
       </c>
-      <c r="AF13" t="n">
-        <v>52.73111081606055</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0.04823526916551885</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0.02662682854553178</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
+      <c r="AQ13" t="n">
+        <v>26.39974039755659</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0.04736060016955471</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0.0286123319295154</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>5.633333333333333</v>
+      </c>
+      <c r="AU13" t="n">
         <v>38</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AV13" t="n">
         <v>229.5333333333333</v>
       </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>12.5977445339462</v>
       </c>
       <c r="AX13" t="n">
-        <v>12.5977445339462</v>
+        <v>0.02578191717598222</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.02538253901292936</v>
+        <v>0.01357322955879181</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.01357322955879181</v>
+        <v>48.23333333333333</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>5.460506332490602</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.9759926642330704</v>
+        <v>0.02844628602689384</v>
       </c>
       <c r="BC13" t="n">
-        <v>10.63737388006907</v>
+        <v>0.01236616715721269</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.02322382889756458</v>
+        <v>32.3</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.01364634454961744</v>
+        <v>7</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>135.9</v>
       </c>
       <c r="BG13" t="n">
+        <v>5.634826831227674</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0.04577908938575968</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0.02941944362946691</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>9.033333333333333</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>10</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>3.329726004813331</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0.03547649060221513</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.02587618030559427</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BQ13" t="n">
         <v>6</v>
       </c>
-      <c r="BH13" t="n">
+      <c r="BR13" t="n">
         <v>30.53333333333333</v>
       </c>
-      <c r="BI13" t="n">
-        <v>11.17029077214659</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.02455984229372332</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.01420973119695834</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM13" t="n">
+      <c r="BS13" t="n">
+        <v>2.917403607793077</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0.04706273838747536</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0.01947674060046173</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>3.433333333333334</v>
+      </c>
+      <c r="BW13" t="n">
         <v>7</v>
       </c>
-      <c r="BN13" t="n">
+      <c r="BX13" t="n">
         <v>46.86666666666667</v>
       </c>
-      <c r="BO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>0</v>
-      </c>
       <c r="BY13" t="n">
-        <v>0</v>
+        <v>10.28510710284104</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0</v>
+        <v>0.01515444361711615</v>
       </c>
       <c r="CA13" t="n">
-        <v>10.28510710284104</v>
+        <v>0.01081936971996877</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.01515444361711615</v>
+        <v>59.7</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.01083928932566791</v>
+        <v>6.01255771060594</v>
       </c>
       <c r="CD13" t="n">
-        <v>0</v>
+        <v>0.01408982021968133</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.9733669184324064</v>
+        <v>0.01011964455966981</v>
       </c>
       <c r="CF13" t="n">
-        <v>9.063799543155163</v>
+        <v>42.66666666666667</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.01502605590698303</v>
+        <v>6</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.0112653157474224</v>
+        <v>79.33333333333333</v>
       </c>
       <c r="CI13" t="n">
-        <v>0</v>
+        <v>2.002902203990025</v>
       </c>
       <c r="CJ13" t="n">
+        <v>0.04626910267546929</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0.03003556776754125</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>3.466666666666667</v>
+      </c>
+      <c r="CM13" t="n">
         <v>5</v>
       </c>
-      <c r="CK13" t="n">
+      <c r="CN13" t="n">
+        <v>35.33333333333334</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>1.666248908871816</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0.03933660128870599</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>0.03329722146170511</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>5</v>
+      </c>
+      <c r="CT13" t="n">
         <v>25.86666666666667</v>
       </c>
-      <c r="CL13" t="n">
-        <v>8.608387301229572</v>
-      </c>
-      <c r="CM13" t="n">
-        <v>0.0142522546405669</v>
-      </c>
-      <c r="CN13" t="n">
-        <v>0.0102133049314328</v>
-      </c>
-      <c r="CO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP13" t="n">
+      <c r="CU13" t="n">
+        <v>2.650803761017582</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>0.01256867256444569</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>0.007671843432743117</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="CY13" t="n">
         <v>5</v>
       </c>
-      <c r="CQ13" t="n">
+      <c r="CZ13" t="n">
         <v>159.4666666666667</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC13" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
+      <c r="A14" s="1" t="n">
+        <v>121</v>
       </c>
       <c r="B14" t="n">
         <v>3</v>
@@ -4447,266 +4313,255 @@
         <v>0.02192471272501467</v>
       </c>
       <c r="W14" t="n">
-        <v>0.01158997995046529</v>
+        <v>0.01154905762356617</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>180.4666666666667</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.9749449493096599</v>
+        <v>11.53556710350807</v>
       </c>
       <c r="Z14" t="n">
-        <v>31.27926903345212</v>
+        <v>0.03643364675951258</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.02675264319836601</v>
+        <v>0.01931094826091555</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.01447065865184383</v>
+        <v>25.93333333333333</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AD14" t="n">
+        <v>215.9</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>13.66378869745556</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.035959008449782</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.02097154142552918</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>292.8</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>13.20896404966011</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.02575393365949118</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.01722020189080383</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="AO14" t="n">
         <v>22</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AP14" t="n">
         <v>168.4</v>
       </c>
-      <c r="AF14" t="n">
-        <v>31.54306582438019</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0.02457601501144646</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0.01403822635458041</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
+      <c r="AQ14" t="n">
+        <v>12.22673212216391</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.02775102028561126</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0.0155540854568569</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>66.10000000000001</v>
+      </c>
+      <c r="AU14" t="n">
         <v>17</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AV14" t="n">
         <v>222.9</v>
       </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>8.157612794819027</v>
       </c>
       <c r="AX14" t="n">
-        <v>8.157612794819027</v>
+        <v>0.01022190427586395</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.01024366981359381</v>
+        <v>0.005334499219157074</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.005336024980534426</v>
+        <v>104.0666666666667</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.594162383899553</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.9732653356913346</v>
+        <v>0.05310141300337866</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.405156755631868</v>
+        <v>0.03779481938118343</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.02582259824485211</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.008639340627938141</v>
+        <v>5</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>105.8</v>
       </c>
       <c r="BG14" t="n">
+        <v>1.124408989675782</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0.06232561075615629</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0.03674641889148559</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK14" t="n">
         <v>3</v>
       </c>
-      <c r="BH14" t="n">
+      <c r="BL14" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>2.205055237304577</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0.01568910407047952</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0.004918763712750351</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR14" t="n">
         <v>14.13333333333333</v>
       </c>
-      <c r="BI14" t="n">
-        <v>5.437260916474533</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>0.009564336687885477</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>0.004962323487391007</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM14" t="n">
+      <c r="BS14" t="n">
+        <v>0.8626824776029833</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0.00740237719809935</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0.005375075800947491</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>27.26666666666667</v>
+      </c>
+      <c r="BW14" t="n">
         <v>2</v>
       </c>
-      <c r="BN14" t="n">
+      <c r="BX14" t="n">
         <v>134.3666666666667</v>
       </c>
-      <c r="BO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>0</v>
-      </c>
       <c r="BY14" t="n">
-        <v>0</v>
+        <v>3.895439737378726</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>0.005200351115991153</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.895439737378726</v>
+        <v>0.002688369594499473</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.00516684729402328</v>
+        <v>198.1666666666667</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.002688369594499473</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
         <v>0</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.9719455675138174</v>
+        <v>0</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.3003966467241286</v>
+        <v>0</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.02678632614609455</v>
+        <v>2</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.03584811235607799</v>
+        <v>76.33333333333333</v>
       </c>
       <c r="CI14" t="n">
         <v>0</v>
       </c>
       <c r="CJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM14" t="n">
         <v>1</v>
       </c>
-      <c r="CK14" t="n">
+      <c r="CN14" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT14" t="n">
         <v>4.933333333333334</v>
       </c>
-      <c r="CL14" t="n">
-        <v>2.420762886533589</v>
-      </c>
-      <c r="CM14" t="n">
-        <v>0.004690246720974844</v>
-      </c>
-      <c r="CN14" t="n">
-        <v>0.00241093071201437</v>
-      </c>
-      <c r="CO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP14" t="n">
+      <c r="CU14" t="n">
+        <v>0.9962299943265174</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>0.00427581285026235</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>0.002023974704600695</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>136.3</v>
+      </c>
+      <c r="CY14" t="n">
         <v>1</v>
       </c>
-      <c r="CQ14" t="n">
+      <c r="CZ14" t="n">
         <v>181.0333333333333</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
+      <c r="A15" s="1" t="n">
+        <v>136</v>
       </c>
       <c r="B15" t="n">
         <v>4</v>
@@ -4787,263 +4642,252 @@
         <v>0.01837970031247294</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>40.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.9731184138056467</v>
+        <v>24.93808364672412</v>
       </c>
       <c r="Z15" t="n">
-        <v>40.64046272069241</v>
+        <v>0.03447098256504812</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.03488859079495965</v>
+        <v>0.01834784491780025</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.01927479593580206</v>
+        <v>25.83333333333334</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AD15" t="n">
+        <v>392.9</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>15.85761601651124</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.03891326563721843</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.0206949802906768</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>16.26666666666667</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>133</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>24.92378669564445</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.03256002270551026</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.01760803478481864</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO15" t="n">
         <v>35</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AP15" t="n">
         <v>289.3</v>
       </c>
-      <c r="AF15" t="n">
-        <v>39.13883991629552</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0.03467503066923405</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0.01877650487869359</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
+      <c r="AQ15" t="n">
+        <v>22.1306387220579</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.03451800677745054</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0.01981419832567503</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>19.06666666666667</v>
+      </c>
+      <c r="AU15" t="n">
         <v>21</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AV15" t="n">
         <v>84.8</v>
       </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>5.956335854726519</v>
       </c>
       <c r="AX15" t="n">
-        <v>5.956335854726519</v>
+        <v>0.01171563195798464</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.01160156325466211</v>
+        <v>0.004587966929581522</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.004550666694098315</v>
+        <v>31.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>0.7613709908037398</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.9665094165033401</v>
+        <v>0.03595440840790476</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.523546836875898</v>
+        <v>0.02322930485534613</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.01070702048400163</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.004156524920231663</v>
+        <v>3</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>64.53333333333333</v>
       </c>
       <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.457257700860932</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0.01292731846320827</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0.005970735080982004</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>6.266666666666667</v>
+      </c>
+      <c r="BQ15" t="n">
         <v>2</v>
       </c>
-      <c r="BH15" t="n">
+      <c r="BR15" t="n">
         <v>231.3666666666667</v>
       </c>
-      <c r="BI15" t="n">
-        <v>0.2202164247396408</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>0.04270991563364479</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>0.01474831509049213</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN15" t="n">
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
         <v>4.1</v>
       </c>
-      <c r="BO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>0</v>
-      </c>
       <c r="BY15" t="n">
-        <v>0</v>
+        <v>6.375570891945425</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>0.01071666587626119</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.375570891945425</v>
+        <v>0.005476143052687288</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.01071666587626119</v>
+        <v>65.7</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.00547926673685617</v>
+        <v>0</v>
       </c>
       <c r="CD15" t="n">
         <v>0</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.9625356161252985</v>
+        <v>0</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.815340886400395</v>
+        <v>0</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.01819967627656593</v>
+        <v>1</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.008793618177052709</v>
+        <v>6.966666666666667</v>
       </c>
       <c r="CI15" t="n">
         <v>0</v>
       </c>
       <c r="CJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>0.749611772791891</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0.03550202926524104</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>0.007846960527652491</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>2.133333333333333</v>
+      </c>
+      <c r="CS15" t="n">
         <v>2</v>
       </c>
-      <c r="CK15" t="n">
+      <c r="CT15" t="n">
         <v>27.63333333333333</v>
       </c>
-      <c r="CL15" t="n">
-        <v>6.375570891945425</v>
-      </c>
-      <c r="CM15" t="n">
-        <v>0.01071666587626119</v>
-      </c>
-      <c r="CN15" t="n">
-        <v>0.00547926673685617</v>
-      </c>
-      <c r="CO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP15" t="n">
+      <c r="CU15" t="n">
+        <v>3.376759572858507</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>0.01006545329075526</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>0.005153653356389396</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>58.26666666666667</v>
+      </c>
+      <c r="CY15" t="n">
         <v>3</v>
       </c>
-      <c r="CQ15" t="n">
+      <c r="CZ15" t="n">
         <v>257.8</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC15" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
+      <c r="A16" s="1" t="n">
+        <v>137</v>
       </c>
       <c r="B16" t="n">
         <v>4</v>
@@ -5124,146 +4968,146 @@
         <v>0.01667532121163273</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>49.06666666666667</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.9683081594536529</v>
+        <v>19.8192767001912</v>
       </c>
       <c r="Z16" t="n">
-        <v>36.01144471394632</v>
+        <v>0.03206081601527432</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.0301743945753068</v>
+        <v>0.01692517879613666</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.01561788320614682</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AD16" t="n">
+        <v>219.1</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>20.42730322129226</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.03416421801161541</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.01893249788815067</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>28.33333333333334</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>243.7666666666667</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>8.962647268601811</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.02629012826664396</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.01395445133098846</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>22.93333333333333</v>
+      </c>
+      <c r="AO16" t="n">
         <v>18</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AP16" t="n">
         <v>215.8</v>
       </c>
-      <c r="AF16" t="n">
-        <v>40.3256319598843</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0.03074456027148309</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0.01636792973388024</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
+      <c r="AQ16" t="n">
+        <v>17.90613991457302</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0.03044835131627312</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0.01660004366951663</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>24.16666666666666</v>
+      </c>
+      <c r="AU16" t="n">
         <v>21</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AV16" t="n">
         <v>221.3333333333333</v>
       </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>5.793526396751433</v>
       </c>
       <c r="AX16" t="n">
-        <v>5.793526396751433</v>
+        <v>0.01117370180140925</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.01117370180140925</v>
+        <v>0.005509549241906275</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.005509549241906275</v>
+        <v>59.26666666666667</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.895062562873437</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.9656320996661435</v>
+        <v>0.03235846466412518</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.918326751276894</v>
+        <v>0.01847851022221891</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.01069984929967538</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.005280919366297931</v>
+        <v>4</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>44.76666666666667</v>
       </c>
       <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>3.481948535903372</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0.009936397140930198</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0.004814490865317489</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>52.36666666666667</v>
+      </c>
+      <c r="BQ16" t="n">
         <v>6</v>
       </c>
-      <c r="BH16" t="n">
+      <c r="BR16" t="n">
         <v>255.2333333333333</v>
       </c>
-      <c r="BI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>0</v>
-      </c>
       <c r="BS16" t="n">
         <v>0</v>
       </c>
@@ -5283,104 +5127,93 @@
         <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>0</v>
+        <v>8.095655110961641</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>0.01555104660360351</v>
       </c>
       <c r="CA16" t="n">
-        <v>8.095655110961641</v>
+        <v>0.007377807418568971</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.01540630664767428</v>
+        <v>39.1</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.007325198643137409</v>
+        <v>1.951152432350268</v>
       </c>
       <c r="CD16" t="n">
-        <v>0</v>
+        <v>0.01820574290155527</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.9565115400534878</v>
+        <v>0.008777478865621285</v>
       </c>
       <c r="CF16" t="n">
-        <v>0.3264964563321002</v>
+        <v>13.43333333333333</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.02703340006851246</v>
+        <v>3</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.01705347713796013</v>
+        <v>84.56666666666666</v>
       </c>
       <c r="CI16" t="n">
-        <v>0</v>
+        <v>4.209621772406882</v>
       </c>
       <c r="CJ16" t="n">
+        <v>0.01615084367166518</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0.008192636680116125</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>4</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>190.5666666666667</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS16" t="n">
         <v>1</v>
       </c>
-      <c r="CK16" t="n">
+      <c r="CT16" t="n">
         <v>7.466666666666667</v>
       </c>
-      <c r="CL16" t="n">
-        <v>1.718988254769815</v>
-      </c>
-      <c r="CM16" t="n">
-        <v>0.01631649043720973</v>
-      </c>
-      <c r="CN16" t="n">
-        <v>0.008800557141844245</v>
-      </c>
-      <c r="CO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP16" t="n">
+      <c r="CU16" t="n">
+        <v>0.7041184983833018</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>0.03990410683840773</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>0.01799549796209643</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>1.133333333333333</v>
+      </c>
+      <c r="CY16" t="n">
         <v>1</v>
       </c>
-      <c r="CQ16" t="n">
+      <c r="CZ16" t="n">
         <v>17.4</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC16" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
+      <c r="A17" s="1" t="n">
+        <v>206</v>
       </c>
       <c r="B17" t="n">
         <v>5</v>
@@ -5464,40 +5297,40 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.9702752070828937</v>
+        <v>55.90911239827313</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>0.06465695071565586</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>0.04057362531050043</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>487.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>43.96473982386986</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>0.05606252075625681</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>0.0355771715327793</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>408.4</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -5536,52 +5369,52 @@
         <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>12.26739707640212</v>
       </c>
       <c r="AX17" t="n">
-        <v>12.26739707640212</v>
+        <v>0.02625058856350287</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.02644769348473242</v>
+        <v>0.01254246553706817</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.01364574370877264</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>8.056629147081985</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.9675680226853323</v>
+        <v>0.02308300887124132</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>0.01243736166144118</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>246.9333333333333</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>3.251684101980183</v>
       </c>
       <c r="BH17" t="n">
-        <v>0</v>
+        <v>0.06234773944831359</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>0.02468655043645513</v>
       </c>
       <c r="BJ17" t="n">
         <v>0</v>
       </c>
       <c r="BK17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BL17" t="n">
-        <v>0</v>
+        <v>53.06666666666667</v>
       </c>
       <c r="BM17" t="n">
         <v>0</v>
@@ -5620,52 +5453,52 @@
         <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>0</v>
+        <v>20.05883336150735</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0</v>
+        <v>0.02558155200990944</v>
       </c>
       <c r="CA17" t="n">
-        <v>20.05883336150735</v>
+        <v>0.01814419499100528</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.02530836592162714</v>
+        <v>2.1</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.01806164551487033</v>
+        <v>14.23902347609019</v>
       </c>
       <c r="CD17" t="n">
-        <v>0</v>
+        <v>0.02505063616160398</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.9616317966861369</v>
+        <v>0.01643759225880174</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="CG17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CH17" t="n">
-        <v>0</v>
+        <v>252.6</v>
       </c>
       <c r="CI17" t="n">
-        <v>0</v>
+        <v>5.74714106017134</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0</v>
+        <v>0.03224731935425088</v>
       </c>
       <c r="CK17" t="n">
-        <v>0</v>
+        <v>0.02565389538419467</v>
       </c>
       <c r="CL17" t="n">
         <v>0</v>
       </c>
       <c r="CM17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="CN17" t="n">
-        <v>0</v>
+        <v>46.9</v>
       </c>
       <c r="CO17" t="n">
         <v>0</v>
@@ -5701,23 +5534,12 @@
         <v>0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
+      <c r="A18" s="1" t="n">
+        <v>207</v>
       </c>
       <c r="B18" t="n">
         <v>5</v>
@@ -5792,49 +5614,49 @@
         <v>55.59168806707446</v>
       </c>
       <c r="V18" t="n">
-        <v>0.04234213981966373</v>
+        <v>0.0426697907337531</v>
       </c>
       <c r="W18" t="n">
-        <v>0.02095508799692103</v>
+        <v>0.0210151551552189</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.9732083250782112</v>
+        <v>32.42594303759552</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>0.04400775806786528</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>0.02422786777269108</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>503.7</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>27.10570374031084</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>0.04082080768942975</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>0.02129993690241992</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>395.8333333333333</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -5873,52 +5695,52 @@
         <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>15.84367080400478</v>
       </c>
       <c r="AX18" t="n">
-        <v>15.84367080400478</v>
+        <v>0.03055565762196094</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.03043381922973998</v>
+        <v>0.01499144003287212</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.01499144003287212</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>9.421915999014084</v>
       </c>
       <c r="BB18" t="n">
-        <v>0.9696022662677553</v>
+        <v>0.02724595111349271</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>0.01236193787773521</v>
       </c>
       <c r="BD18" t="n">
         <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>229.0333333333333</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>6.569277633650209</v>
       </c>
       <c r="BH18" t="n">
-        <v>0</v>
+        <v>0.05737506535129979</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>0.04549865757863666</v>
       </c>
       <c r="BJ18" t="n">
         <v>0</v>
       </c>
       <c r="BK18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BL18" t="n">
-        <v>0</v>
+        <v>70.93333333333334</v>
       </c>
       <c r="BM18" t="n">
         <v>0</v>
@@ -5957,52 +5779,52 @@
         <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>0</v>
+        <v>60.06436242473152</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0</v>
+        <v>0.06420025400250828</v>
       </c>
       <c r="CA18" t="n">
-        <v>60.06436242473152</v>
+        <v>0.03775809586814749</v>
       </c>
       <c r="CB18" t="n">
-        <v>0.06525482760102388</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="CC18" t="n">
-        <v>0.03711453003901799</v>
+        <v>46.32766557413458</v>
       </c>
       <c r="CD18" t="n">
-        <v>0</v>
+        <v>0.06314890119537635</v>
       </c>
       <c r="CE18" t="n">
-        <v>0.9581462438665009</v>
+        <v>0.07055778184086146</v>
       </c>
       <c r="CF18" t="n">
-        <v>0</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="CG18" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CH18" t="n">
-        <v>0</v>
+        <v>170.6666666666667</v>
       </c>
       <c r="CI18" t="n">
-        <v>0</v>
+        <v>19.31206728960206</v>
       </c>
       <c r="CJ18" t="n">
-        <v>0</v>
+        <v>0.06495135074092213</v>
       </c>
       <c r="CK18" t="n">
-        <v>0</v>
+        <v>0.05061470930929395</v>
       </c>
       <c r="CL18" t="n">
-        <v>0</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="CM18" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="CN18" t="n">
-        <v>0</v>
+        <v>128.5</v>
       </c>
       <c r="CO18" t="n">
         <v>0</v>
@@ -6038,23 +5860,12 @@
         <v>0</v>
       </c>
       <c r="CZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
+      <c r="A19" s="1" t="n">
+        <v>210</v>
       </c>
       <c r="B19" t="n">
         <v>6</v>
@@ -6132,46 +5943,46 @@
         <v>0.06544367497748241</v>
       </c>
       <c r="W19" t="n">
-        <v>0.034292055680331</v>
+        <v>0.03446544875094415</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.9629875074412707</v>
+        <v>53.36610381472785</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>0.0609222185444746</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>0.03659903614164115</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>673.7333333333333</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>39.26342493147088</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>0.06649636454611438</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>0.03520349250447819</v>
       </c>
       <c r="AH19" t="n">
         <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>223.7333333333333</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -6210,52 +6021,52 @@
         <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>21.65798320740409</v>
       </c>
       <c r="AX19" t="n">
-        <v>21.65798320740409</v>
+        <v>0.05697613936600537</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.05697613936600537</v>
+        <v>0.03068026809443747</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.03068026809443747</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>15.81048152683326</v>
       </c>
       <c r="BB19" t="n">
-        <v>0.9649021291781464</v>
+        <v>0.05445506480203302</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>0.02710229662296226</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>209.7666666666667</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>9.182160533586677</v>
       </c>
       <c r="BH19" t="n">
-        <v>0</v>
+        <v>0.05026152300786954</v>
       </c>
       <c r="BI19" t="n">
-        <v>0</v>
+        <v>0.02885085734642907</v>
       </c>
       <c r="BJ19" t="n">
         <v>0</v>
       </c>
       <c r="BK19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BL19" t="n">
-        <v>0</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="BM19" t="n">
         <v>0</v>
@@ -6294,52 +6105,52 @@
         <v>0</v>
       </c>
       <c r="BY19" t="n">
-        <v>0</v>
+        <v>53.44393296023298</v>
       </c>
       <c r="BZ19" t="n">
-        <v>0</v>
+        <v>0.05146169287406993</v>
       </c>
       <c r="CA19" t="n">
-        <v>53.44393296023298</v>
+        <v>0.04212645931901238</v>
       </c>
       <c r="CB19" t="n">
-        <v>0.05207358363252285</v>
+        <v>2.233333333333333</v>
       </c>
       <c r="CC19" t="n">
-        <v>0.04244245562778026</v>
+        <v>47.42245869699392</v>
       </c>
       <c r="CD19" t="n">
-        <v>0</v>
+        <v>0.06464010855787528</v>
       </c>
       <c r="CE19" t="n">
-        <v>0.9596241730701607</v>
+        <v>0.06099104099348358</v>
       </c>
       <c r="CF19" t="n">
-        <v>0</v>
+        <v>2.233333333333333</v>
       </c>
       <c r="CG19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="CH19" t="n">
-        <v>0</v>
+        <v>226.2333333333333</v>
       </c>
       <c r="CI19" t="n">
-        <v>0</v>
+        <v>27.6979139625672</v>
       </c>
       <c r="CJ19" t="n">
-        <v>0</v>
+        <v>0.05395340203291675</v>
       </c>
       <c r="CK19" t="n">
-        <v>0</v>
+        <v>0.04171895750744947</v>
       </c>
       <c r="CL19" t="n">
         <v>0</v>
       </c>
       <c r="CM19" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="CN19" t="n">
-        <v>0</v>
+        <v>71.83333333333333</v>
       </c>
       <c r="CO19" t="n">
         <v>0</v>
@@ -6375,23 +6186,12 @@
         <v>0</v>
       </c>
       <c r="CZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
+      <c r="A20" s="1" t="n">
+        <v>211</v>
       </c>
       <c r="B20" t="n">
         <v>6</v>
@@ -6472,43 +6272,43 @@
         <v>0.01869082033334679</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.9776499591644092</v>
+        <v>28.57583712927257</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>0.03852006607600101</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>0.02138024843894372</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>534.3666666666667</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>19.08223607065278</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>0.04206408338618707</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>0.02198826575279376</v>
       </c>
       <c r="AH20" t="n">
         <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>365.6333333333333</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -6547,52 +6347,52 @@
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>9.841456765100189</v>
       </c>
       <c r="AX20" t="n">
-        <v>9.841456765100189</v>
+        <v>0.01769860324950839</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.01764415575311545</v>
+        <v>0.007445635538748996</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.007194978044874567</v>
+        <v>5.266666666666667</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>6.54415189937121</v>
       </c>
       <c r="BB20" t="n">
-        <v>0.9654722237431199</v>
+        <v>0.02226030160145744</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>0.009452343742184878</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>3.133333333333334</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>281.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>1.348572975604115</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>0.05905987929864782</v>
       </c>
       <c r="BI20" t="n">
-        <v>0</v>
+        <v>0.04525551830895137</v>
       </c>
       <c r="BJ20" t="n">
         <v>0</v>
       </c>
       <c r="BK20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BL20" t="n">
-        <v>0</v>
+        <v>18.43333333333333</v>
       </c>
       <c r="BM20" t="n">
         <v>0</v>
@@ -6631,52 +6431,52 @@
         <v>0</v>
       </c>
       <c r="BY20" t="n">
-        <v>0</v>
+        <v>19.109121366101</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0</v>
+        <v>0.01349331000169085</v>
       </c>
       <c r="CA20" t="n">
-        <v>19.109121366101</v>
+        <v>0.004224023538283217</v>
       </c>
       <c r="CB20" t="n">
-        <v>0.01349331000169085</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="CC20" t="n">
-        <v>0.004171337026212529</v>
+        <v>13.82706143841464</v>
       </c>
       <c r="CD20" t="n">
-        <v>0</v>
+        <v>0.01749293264828461</v>
       </c>
       <c r="CE20" t="n">
-        <v>0.9652516832378912</v>
+        <v>0.02062598604791473</v>
       </c>
       <c r="CF20" t="n">
-        <v>0</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="CG20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="CH20" t="n">
-        <v>0</v>
+        <v>269.3333333333333</v>
       </c>
       <c r="CI20" t="n">
-        <v>0</v>
+        <v>4.845798402772902</v>
       </c>
       <c r="CJ20" t="n">
-        <v>0</v>
+        <v>0.09259699479760589</v>
       </c>
       <c r="CK20" t="n">
-        <v>0</v>
+        <v>0.05677338973045286</v>
       </c>
       <c r="CL20" t="n">
         <v>0</v>
       </c>
       <c r="CM20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CN20" t="n">
-        <v>0</v>
+        <v>28.3</v>
       </c>
       <c r="CO20" t="n">
         <v>0</v>
@@ -6712,41 +6512,32 @@
         <v>0</v>
       </c>
       <c r="CZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC20" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B1:T1"/>
-    <mergeCell ref="U1:AW1"/>
-    <mergeCell ref="AX1:BZ1"/>
-    <mergeCell ref="CA1:DC1"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:T1"/>
+    <mergeCell ref="U1:AV1"/>
+    <mergeCell ref="AW1:BX1"/>
+    <mergeCell ref="BY1:CZ1"/>
     <mergeCell ref="F2:H2"/>
-    <mergeCell ref="J2:T2"/>
     <mergeCell ref="U2:X2"/>
-    <mergeCell ref="Z2:AE2"/>
-    <mergeCell ref="AF2:AK2"/>
-    <mergeCell ref="AL2:AQ2"/>
-    <mergeCell ref="AR2:AW2"/>
-    <mergeCell ref="AX2:BA2"/>
-    <mergeCell ref="BC2:BH2"/>
-    <mergeCell ref="BI2:BN2"/>
-    <mergeCell ref="BO2:BT2"/>
-    <mergeCell ref="BU2:BZ2"/>
-    <mergeCell ref="CA2:CD2"/>
-    <mergeCell ref="CF2:CK2"/>
-    <mergeCell ref="CL2:CQ2"/>
-    <mergeCell ref="CR2:CW2"/>
-    <mergeCell ref="CX2:DC2"/>
+    <mergeCell ref="Y2:AD2"/>
+    <mergeCell ref="AE2:AJ2"/>
+    <mergeCell ref="AK2:AP2"/>
+    <mergeCell ref="AQ2:AV2"/>
+    <mergeCell ref="AW2:AZ2"/>
+    <mergeCell ref="BA2:BF2"/>
+    <mergeCell ref="BG2:BL2"/>
+    <mergeCell ref="BM2:BR2"/>
+    <mergeCell ref="BS2:BX2"/>
+    <mergeCell ref="BY2:CB2"/>
+    <mergeCell ref="CC2:CH2"/>
+    <mergeCell ref="CI2:CN2"/>
+    <mergeCell ref="CO2:CT2"/>
+    <mergeCell ref="CU2:CZ2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/examples/sequence/OUL/result/animal_id_indexed_result_data-5.xlsx
+++ b/examples/sequence/OUL/result/animal_id_indexed_result_data-5.xlsx
@@ -457,25 +457,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>SecondsObserving</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
       <c r="F1" s="1" t="n"/>
       <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
       <c r="I1" s="1" t="n"/>
       <c r="J1" s="1" t="n"/>
       <c r="K1" s="1" t="n"/>
       <c r="L1" s="1" t="n"/>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>ObjectsInUpdatingLocationsTrainingTrial</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="N1" s="1" t="n"/>
@@ -507,7 +519,7 @@
       <c r="AN1" s="1" t="n"/>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>ObjectsInUpdatingLocationsUpdateTrial</t>
+          <t>Update</t>
         </is>
       </c>
       <c r="AP1" s="1" t="n"/>
@@ -539,7 +551,7 @@
       <c r="BP1" s="1" t="n"/>
       <c r="BQ1" s="1" t="inlineStr">
         <is>
-          <t>ObjectsInUpdatingLocationsTestTrial</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="BR1" s="1" t="n"/>
@@ -571,62 +583,34 @@
       <c r="CR1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr"/>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>object_1</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>object_2</t>
-        </is>
-      </c>
+          <t>SecondsObserving</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>object_1</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>object_4</t>
-        </is>
-      </c>
+          <t>SecondsObserving</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>object_1</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>object_2</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>object_3</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>object_4</t>
-        </is>
-      </c>
+          <t>SecondsObserving</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
       <c r="M2" s="1" t="inlineStr">
         <is>
           <t>All</t>
@@ -773,18 +757,66 @@
       <c r="CR2" s="1" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr"/>
-      <c r="B3" s="1" t="inlineStr"/>
-      <c r="C3" s="1" t="inlineStr"/>
-      <c r="D3" s="1" t="inlineStr"/>
-      <c r="E3" s="1" t="inlineStr"/>
-      <c r="F3" s="1" t="inlineStr"/>
-      <c r="G3" s="1" t="inlineStr"/>
-      <c r="H3" s="1" t="inlineStr"/>
-      <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr"/>
-      <c r="K3" s="1" t="inlineStr"/>
-      <c r="L3" s="1" t="inlineStr"/>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Location/Category</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>object_1</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>object_2</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>object_1</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>object_4</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>object_1</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>object_2</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>object_3</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>object_4</t>
+        </is>
+      </c>
       <c r="M3" s="1" t="inlineStr">
         <is>
           <t>Displacement</t>
@@ -1220,49 +1252,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52.93333333333333</v>
+        <v>63.73333333333333</v>
       </c>
       <c r="C5" t="n">
-        <v>16.83333333333333</v>
+        <v>32.2</v>
       </c>
       <c r="D5" t="n">
-        <v>17.26666666666667</v>
+        <v>31.93333333333333</v>
       </c>
       <c r="E5" t="n">
-        <v>10.7</v>
+        <v>15.43333333333333</v>
       </c>
       <c r="F5" t="n">
-        <v>1.766666666666667</v>
+        <v>3.966666666666667</v>
       </c>
       <c r="G5" t="n">
-        <v>5.633333333333334</v>
+        <v>11.46666666666667</v>
       </c>
       <c r="H5" t="n">
-        <v>8.800000000000001</v>
+        <v>10.93333333333333</v>
       </c>
       <c r="I5" t="n">
-        <v>3.833333333333333</v>
+        <v>6.5</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2.166666666666667</v>
+        <v>4.433333333333334</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>41.74605650683903</v>
+        <v>41.64610706718376</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03441682216631714</v>
+        <v>0.03471899028861597</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01985000168820161</v>
+        <v>0.01990920743786628</v>
       </c>
       <c r="P5" t="n">
-        <v>84.73333333333333</v>
+        <v>82.5</v>
       </c>
       <c r="Q5" t="n">
         <v>19.91259656031206</v>
@@ -1298,7 +1330,7 @@
         <v>48</v>
       </c>
       <c r="AB5" t="n">
-        <v>391.8</v>
+        <v>384.2333333333333</v>
       </c>
       <c r="AC5" t="n">
         <v>18.41187174601959</v>
@@ -1337,16 +1369,16 @@
         <v>176.7666666666667</v>
       </c>
       <c r="AO5" t="n">
-        <v>9.283426819300228</v>
+        <v>9.22396391468482</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.01482247628286548</v>
+        <v>0.01487704050104988</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.008629452147732364</v>
+        <v>0.008874554751206354</v>
       </c>
       <c r="AR5" t="n">
-        <v>71.06666666666666</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AS5" t="n">
         <v>2.933845526590064</v>
@@ -1400,7 +1432,7 @@
         <v>12</v>
       </c>
       <c r="BJ5" t="n">
-        <v>215.1666666666667</v>
+        <v>207.7333333333333</v>
       </c>
       <c r="BK5" t="n">
         <v>3.35473956765333</v>
@@ -1421,16 +1453,16 @@
         <v>46.96666666666667</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.36481376403658</v>
+        <v>8.334471379224659</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.01310903564999227</v>
+        <v>0.01324476956876547</v>
       </c>
       <c r="BS5" t="n">
         <v>0.008334823185184859</v>
       </c>
       <c r="BT5" t="n">
-        <v>95.13333333333334</v>
+        <v>91.83333333333333</v>
       </c>
       <c r="BU5" t="n">
         <v>1.760401513616138</v>
@@ -1466,7 +1498,7 @@
         <v>6</v>
       </c>
       <c r="CF5" t="n">
-        <v>192.3666666666667</v>
+        <v>188.8333333333333</v>
       </c>
       <c r="CG5" t="n">
         <v>0.8009933812336619</v>
@@ -1512,46 +1544,46 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25.96666666666667</v>
+        <v>31.06666666666667</v>
       </c>
       <c r="C6" t="n">
-        <v>7.033333333333333</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="D6" t="n">
-        <v>11.03333333333333</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="n">
-        <v>11.43333333333333</v>
+        <v>13.8</v>
       </c>
       <c r="F6" t="n">
-        <v>1.433333333333333</v>
+        <v>2.9</v>
       </c>
       <c r="G6" t="n">
-        <v>5.766666666666667</v>
+        <v>10.9</v>
       </c>
       <c r="H6" t="n">
-        <v>10.16666666666667</v>
+        <v>9.566666666666666</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9333333333333333</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="K6" t="n">
-        <v>1.133333333333333</v>
+        <v>1.766666666666667</v>
       </c>
       <c r="L6" t="n">
-        <v>2.733333333333333</v>
+        <v>4.1</v>
       </c>
       <c r="M6" t="n">
-        <v>29.48172281741979</v>
+        <v>29.32641339525763</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02075099630905619</v>
+        <v>0.02073041789825814</v>
       </c>
       <c r="O6" t="n">
-        <v>0.009487789705372451</v>
+        <v>0.009464159185873289</v>
       </c>
       <c r="P6" t="n">
         <v>196.4333333333333</v>
@@ -1587,10 +1619,10 @@
         <v>53.36666666666667</v>
       </c>
       <c r="AA6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB6" t="n">
-        <v>171.6333333333333</v>
+        <v>171.1666666666667</v>
       </c>
       <c r="AC6" t="n">
         <v>9.350823691506598</v>
@@ -1611,34 +1643,34 @@
         <v>104.7666666666667</v>
       </c>
       <c r="AI6" t="n">
-        <v>14.35847827356003</v>
+        <v>14.0010055044801</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.01704247359475292</v>
+        <v>0.01672322492144378</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.009348786484080298</v>
+        <v>0.009030134075669709</v>
       </c>
       <c r="AL6" t="n">
         <v>189.6333333333333</v>
       </c>
       <c r="AM6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AN6" t="n">
-        <v>561.6666666666666</v>
+        <v>557.6666666666666</v>
       </c>
       <c r="AO6" t="n">
-        <v>8.039212460136646</v>
+        <v>7.988205916506674</v>
       </c>
       <c r="AP6" t="n">
         <v>0.01041436134319029</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.006166483992665839</v>
+        <v>0.00612516053119716</v>
       </c>
       <c r="AR6" t="n">
-        <v>91.56666666666666</v>
+        <v>90.43333333333334</v>
       </c>
       <c r="AS6" t="n">
         <v>0.4789796662596689</v>
@@ -1710,19 +1742,19 @@
         <v>8</v>
       </c>
       <c r="BP6" t="n">
-        <v>76.59999999999999</v>
+        <v>73.43333333333334</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7.100624440708097</v>
+        <v>6.561089345843578</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.00889862807749997</v>
+        <v>0.008649673847713979</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.004149256608989571</v>
+        <v>0.003852337924094673</v>
       </c>
       <c r="BT6" t="n">
-        <v>106.0333333333333</v>
+        <v>104.9666666666667</v>
       </c>
       <c r="BU6" t="n">
         <v>0.6635934138896212</v>
@@ -1737,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BZ6" t="n">
-        <v>18.7</v>
+        <v>13.93333333333333</v>
       </c>
       <c r="CA6" t="n">
         <v>0</v>
@@ -1761,22 +1793,22 @@
         <v>15</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.959470840411681</v>
+        <v>3.44252648194009</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.02159092923777074</v>
+        <v>0.0200541535552981</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.01007965156166292</v>
+        <v>0.009448371212903902</v>
       </c>
       <c r="CJ6" t="n">
-        <v>36.46666666666667</v>
+        <v>35.23333333333333</v>
       </c>
       <c r="CK6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CL6" t="n">
-        <v>94.66666666666667</v>
+        <v>88.23333333333333</v>
       </c>
       <c r="CM6" t="n">
         <v>1.498278251678266</v>
@@ -1804,67 +1836,67 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>60.8</v>
+        <v>72.83333333333333</v>
       </c>
       <c r="C7" t="n">
-        <v>21.23333333333333</v>
+        <v>35.8</v>
       </c>
       <c r="D7" t="n">
-        <v>20.8</v>
+        <v>37.03333333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>10.83333333333333</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="F7" t="n">
-        <v>4.266666666666667</v>
+        <v>7.566666666666666</v>
       </c>
       <c r="G7" t="n">
-        <v>2.433333333333333</v>
+        <v>4.6</v>
       </c>
       <c r="H7" t="n">
-        <v>2.033333333333333</v>
+        <v>2.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8666666666666667</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.633333333333333</v>
+        <v>2.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>55.90015376642269</v>
+        <v>55.38335443378686</v>
       </c>
       <c r="N7" t="n">
-        <v>0.04935888036540859</v>
+        <v>0.04937641824826922</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02501099413053598</v>
+        <v>0.02486203116638319</v>
       </c>
       <c r="P7" t="n">
-        <v>30.76666666666667</v>
+        <v>28.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>23.88026789596322</v>
+        <v>23.22893002863071</v>
       </c>
       <c r="R7" t="n">
-        <v>0.05700929644865459</v>
+        <v>0.05624327328421783</v>
       </c>
       <c r="S7" t="n">
-        <v>0.03393394479368328</v>
+        <v>0.03423340877765096</v>
       </c>
       <c r="T7" t="n">
         <v>6.600000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="V7" t="n">
-        <v>255.6</v>
+        <v>250.9</v>
       </c>
       <c r="W7" t="n">
         <v>35.30647316603013</v>
@@ -1897,10 +1929,10 @@
         <v>3.266666666666667</v>
       </c>
       <c r="AG7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AH7" t="n">
-        <v>202.2666666666667</v>
+        <v>198.5</v>
       </c>
       <c r="AI7" t="n">
         <v>24.77335040124394</v>
@@ -1921,34 +1953,34 @@
         <v>162.6</v>
       </c>
       <c r="AO7" t="n">
-        <v>13.92959785928277</v>
+        <v>13.6249587760918</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.03501834414197058</v>
+        <v>0.03408813116483894</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.01634698944535118</v>
+        <v>0.01631121800585456</v>
       </c>
       <c r="AR7" t="n">
         <v>15.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.808999349326784</v>
+        <v>6.467085751736003</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.02697420356831161</v>
+        <v>0.02598692758284815</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.01246791775456714</v>
+        <v>0.01208924406223636</v>
       </c>
       <c r="AV7" t="n">
         <v>11.26666666666667</v>
       </c>
       <c r="AW7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX7" t="n">
-        <v>113.5666666666667</v>
+        <v>111.1</v>
       </c>
       <c r="AY7" t="n">
         <v>4.746609092482614</v>
@@ -1969,22 +2001,22 @@
         <v>81.40000000000001</v>
       </c>
       <c r="BE7" t="n">
-        <v>3.391593270597467</v>
+        <v>2.865778907677246</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.0292546678580577</v>
+        <v>0.02872573558650411</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.01619115018234137</v>
+        <v>0.01471469634723973</v>
       </c>
       <c r="BH7" t="n">
         <v>3.233333333333333</v>
       </c>
       <c r="BI7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BJ7" t="n">
-        <v>94.09999999999999</v>
+        <v>91.26666666666667</v>
       </c>
       <c r="BK7" t="n">
         <v>0.9809092316451562</v>
@@ -2005,13 +2037,13 @@
         <v>16.23333333333333</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7.382962807174497</v>
+        <v>7.102756829337438</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.01207087195718398</v>
+        <v>0.01180711741611767</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.00617191986744936</v>
+        <v>0.005953698936633778</v>
       </c>
       <c r="BT7" t="n">
         <v>73.09999999999999</v>
@@ -2047,10 +2079,10 @@
         <v>30.46666666666667</v>
       </c>
       <c r="CE7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CF7" t="n">
-        <v>113.0666666666667</v>
+        <v>109.3333333333333</v>
       </c>
       <c r="CG7" t="n">
         <v>0.3923913936524657</v>
@@ -2071,22 +2103,22 @@
         <v>60.13333333333333</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.3371919230969136</v>
+        <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.04760028377704029</v>
+        <v>0</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.006600953082981142</v>
+        <v>0</v>
       </c>
       <c r="CP7" t="n">
         <v>0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CR7" t="n">
-        <v>9.800000000000001</v>
+        <v>7.833333333333333</v>
       </c>
     </row>
     <row r="8">
@@ -2096,46 +2128,46 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18.66666666666667</v>
+        <v>21.3</v>
       </c>
       <c r="C8" t="n">
-        <v>8.333333333333334</v>
+        <v>15.26666666666667</v>
       </c>
       <c r="D8" t="n">
-        <v>3.866666666666667</v>
+        <v>6.033333333333333</v>
       </c>
       <c r="E8" t="n">
-        <v>6.666666666666667</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="F8" t="n">
-        <v>1.233333333333333</v>
+        <v>1.966666666666667</v>
       </c>
       <c r="G8" t="n">
-        <v>3.166666666666667</v>
+        <v>5.366666666666666</v>
       </c>
       <c r="H8" t="n">
-        <v>10.86666666666667</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4</v>
+        <v>2.866666666666667</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5</v>
+        <v>2.966666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>28.02158758532409</v>
+        <v>27.83636074402031</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0198847400422939</v>
+        <v>0.01971157163780407</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0102927605214263</v>
+        <v>0.0102509016613459</v>
       </c>
       <c r="P8" t="n">
         <v>167.2666666666667</v>
@@ -2192,7 +2224,7 @@
         <v>8</v>
       </c>
       <c r="AH8" t="n">
-        <v>58</v>
+        <v>52.96666666666667</v>
       </c>
       <c r="AI8" t="n">
         <v>8.723015995762534</v>
@@ -2213,16 +2245,16 @@
         <v>107.1666666666667</v>
       </c>
       <c r="AO8" t="n">
-        <v>4.825305605105349</v>
+        <v>4.816383239319964</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.00778685106575544</v>
+        <v>0.007805555219233429</v>
       </c>
       <c r="AQ8" t="n">
         <v>0.004480356421169063</v>
       </c>
       <c r="AR8" t="n">
-        <v>126.0666666666667</v>
+        <v>124.9333333333333</v>
       </c>
       <c r="AS8" t="n">
         <v>0.3401098041650448</v>
@@ -2258,7 +2290,7 @@
         <v>7</v>
       </c>
       <c r="BD8" t="n">
-        <v>226.0666666666667</v>
+        <v>224.2</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -2297,16 +2329,16 @@
         <v>11.13333333333333</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.140586760405684</v>
+        <v>6.994180242354367</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.008673701219803875</v>
+        <v>0.009120356188553114</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.004707185258567059</v>
+        <v>0.004957857292652967</v>
       </c>
       <c r="BT8" t="n">
-        <v>136.5666666666667</v>
+        <v>117.6333333333333</v>
       </c>
       <c r="BU8" t="n">
         <v>0.6488721468059869</v>
@@ -2342,7 +2374,7 @@
         <v>4</v>
       </c>
       <c r="CF8" t="n">
-        <v>195.3333333333333</v>
+        <v>171.8666666666667</v>
       </c>
       <c r="CG8" t="n">
         <v>0.6451646618143619</v>
@@ -2388,46 +2420,46 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>40.8</v>
+        <v>53.93333333333333</v>
       </c>
       <c r="C9" t="n">
-        <v>8.6</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>20.3</v>
+        <v>36.93333333333333</v>
       </c>
       <c r="E9" t="n">
-        <v>10.66666666666667</v>
+        <v>14.1</v>
       </c>
       <c r="F9" t="n">
-        <v>3.566666666666667</v>
+        <v>7.8</v>
       </c>
       <c r="G9" t="n">
-        <v>3.4</v>
+        <v>6.3</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>9.433333333333334</v>
       </c>
       <c r="I9" t="n">
-        <v>1.466666666666667</v>
+        <v>2.8</v>
       </c>
       <c r="J9" t="n">
-        <v>1.633333333333333</v>
+        <v>3.1</v>
       </c>
       <c r="K9" t="n">
-        <v>1.833333333333333</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.333333333333333</v>
+        <v>3.533333333333333</v>
       </c>
       <c r="M9" t="n">
-        <v>52.67386694193895</v>
+        <v>52.23370658340453</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04549831993760167</v>
+        <v>0.04547210591476281</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02322529299606674</v>
+        <v>0.02292144226232762</v>
       </c>
       <c r="P9" t="n">
         <v>18.93333333333333</v>
@@ -2451,22 +2483,22 @@
         <v>200.5</v>
       </c>
       <c r="W9" t="n">
-        <v>25.97709243921111</v>
+        <v>25.54881599919044</v>
       </c>
       <c r="X9" t="n">
-        <v>0.05085383993208458</v>
+        <v>0.05114689694332212</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0304005197175334</v>
+        <v>0.03049161849621586</v>
       </c>
       <c r="Z9" t="n">
         <v>3.266666666666667</v>
       </c>
       <c r="AA9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AB9" t="n">
-        <v>238.0333333333333</v>
+        <v>237.6</v>
       </c>
       <c r="AC9" t="n">
         <v>23.5584377169756</v>
@@ -2487,31 +2519,31 @@
         <v>242.2</v>
       </c>
       <c r="AI9" t="n">
-        <v>19.13064491099405</v>
+        <v>18.94714365678205</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.04346124237084045</v>
+        <v>0.04380418199678147</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.02345902801376267</v>
+        <v>0.02375697947771433</v>
       </c>
       <c r="AL9" t="n">
         <v>9.166666666666668</v>
       </c>
       <c r="AM9" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AN9" t="n">
-        <v>223.9333333333333</v>
+        <v>219.7</v>
       </c>
       <c r="AO9" t="n">
-        <v>12.95743543148369</v>
+        <v>12.89270467502311</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.025715015032302</v>
+        <v>0.02579878549384312</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.01336579056538667</v>
+        <v>0.01359264625897838</v>
       </c>
       <c r="AR9" t="n">
         <v>49.23333333333333</v>
@@ -2532,7 +2564,7 @@
         <v>10</v>
       </c>
       <c r="AX9" t="n">
-        <v>86.76666666666667</v>
+        <v>83.83333333333333</v>
       </c>
       <c r="AY9" t="n">
         <v>5.877791982481521</v>
@@ -2589,13 +2621,13 @@
         <v>33.46666666666667</v>
       </c>
       <c r="BQ9" t="n">
-        <v>10.79670460148499</v>
+        <v>10.23775594095652</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.01640770755182397</v>
+        <v>0.01604174890593058</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.01266928590363769</v>
+        <v>0.0118202001542258</v>
       </c>
       <c r="BT9" t="n">
         <v>64.3</v>
@@ -2631,10 +2663,10 @@
         <v>59.9</v>
       </c>
       <c r="CE9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CF9" t="n">
-        <v>86.7</v>
+        <v>78.5</v>
       </c>
       <c r="CG9" t="n">
         <v>2.865772435930864</v>
@@ -2655,22 +2687,22 @@
         <v>160.7333333333333</v>
       </c>
       <c r="CM9" t="n">
-        <v>3.285568778741376</v>
+        <v>1.704577236637729</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.02999822238492474</v>
+        <v>0.04196917621986464</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.02682645706156396</v>
+        <v>0.03747864955846146</v>
       </c>
       <c r="CP9" t="n">
-        <v>10.23333333333333</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="CQ9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CR9" t="n">
-        <v>30.56666666666667</v>
+        <v>27.53333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -2680,49 +2712,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29.33333333333333</v>
+        <v>38.76666666666667</v>
       </c>
       <c r="C10" t="n">
-        <v>8.9</v>
+        <v>18.33333333333333</v>
       </c>
       <c r="D10" t="n">
-        <v>9.433333333333334</v>
+        <v>20.43333333333333</v>
       </c>
       <c r="E10" t="n">
-        <v>5.3</v>
+        <v>5.966666666666667</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5</v>
+        <v>2.966666666666667</v>
       </c>
       <c r="G10" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6</v>
+        <v>1.766666666666667</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5333333333333333</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.033333333333333</v>
+        <v>1.766666666666667</v>
       </c>
       <c r="M10" t="n">
-        <v>33.63620914717328</v>
+        <v>33.60033318472292</v>
       </c>
       <c r="N10" t="n">
-        <v>0.02194874845989059</v>
+        <v>0.02209747861367783</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01205542042516417</v>
+        <v>0.01213590607593518</v>
       </c>
       <c r="P10" t="n">
-        <v>198.1</v>
+        <v>196.9333333333333</v>
       </c>
       <c r="Q10" t="n">
         <v>13.02681135360724</v>
@@ -2740,7 +2772,7 @@
         <v>23</v>
       </c>
       <c r="V10" t="n">
-        <v>280.9333333333333</v>
+        <v>277.4</v>
       </c>
       <c r="W10" t="n">
         <v>11.56713532767809</v>
@@ -2797,16 +2829,16 @@
         <v>187.1</v>
       </c>
       <c r="AO10" t="n">
-        <v>7.962827648965044</v>
+        <v>7.944781641680085</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.0114855597144724</v>
+        <v>0.01151389175030326</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.007637856984049951</v>
+        <v>0.007617627879009659</v>
       </c>
       <c r="AR10" t="n">
-        <v>104.1333333333333</v>
+        <v>102.7333333333333</v>
       </c>
       <c r="AS10" t="n">
         <v>0.9427607096399984</v>
@@ -2842,7 +2874,7 @@
         <v>6</v>
       </c>
       <c r="BD10" t="n">
-        <v>107</v>
+        <v>104.8666666666667</v>
       </c>
       <c r="BE10" t="n">
         <v>0.94802622737229</v>
@@ -2881,16 +2913,16 @@
         <v>16.83333333333333</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.119967174629809</v>
+        <v>3.998802301134913</v>
       </c>
       <c r="BR10" t="n">
         <v>0.005243113065948268</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.003962802636501173</v>
+        <v>0.003914788539268965</v>
       </c>
       <c r="BT10" t="n">
-        <v>206.7333333333333</v>
+        <v>195.0333333333333</v>
       </c>
       <c r="BU10" t="n">
         <v>0</v>
@@ -2926,7 +2958,7 @@
         <v>2</v>
       </c>
       <c r="CF10" t="n">
-        <v>93.3</v>
+        <v>76.13333333333334</v>
       </c>
       <c r="CG10" t="n">
         <v>1.165015762287421</v>
@@ -2972,46 +3004,46 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.46666666666667</v>
+        <v>33.53333333333333</v>
       </c>
       <c r="C11" t="n">
-        <v>9.933333333333334</v>
+        <v>18.93333333333333</v>
       </c>
       <c r="D11" t="n">
-        <v>5.833333333333333</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="n">
-        <v>1.266666666666667</v>
+        <v>2.566666666666667</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.166666666666667</v>
+        <v>2.566666666666667</v>
       </c>
       <c r="H11" t="n">
-        <v>2.7</v>
+        <v>3.033333333333333</v>
       </c>
       <c r="I11" t="n">
-        <v>1.566666666666667</v>
+        <v>3.033333333333333</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4333333333333333</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7333333333333333</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1.066666666666667</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>39.88751736501784</v>
+        <v>39.75867346159802</v>
       </c>
       <c r="N11" t="n">
         <v>0.03320555416781201</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01831956377491517</v>
+        <v>0.01834670277550754</v>
       </c>
       <c r="P11" t="n">
         <v>47.16666666666666</v>
@@ -3086,16 +3118,16 @@
         <v>37</v>
       </c>
       <c r="AN11" t="n">
-        <v>313.1666666666667</v>
+        <v>309.5333333333334</v>
       </c>
       <c r="AO11" t="n">
-        <v>5.781507170331728</v>
+        <v>5.480970436487546</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.01125175350956287</v>
+        <v>0.01109904888237678</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.003807849512903305</v>
+        <v>0.003767840452058691</v>
       </c>
       <c r="AR11" t="n">
         <v>26.13333333333333</v>
@@ -3131,10 +3163,10 @@
         <v>1.233333333333333</v>
       </c>
       <c r="BC11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD11" t="n">
-        <v>64.86666666666666</v>
+        <v>63.93333333333333</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -3155,34 +3187,34 @@
         <v>3.9</v>
       </c>
       <c r="BK11" t="n">
-        <v>3.594559906792144</v>
+        <v>1.399491542568836</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.01038091882564966</v>
+        <v>0.0115177344672428</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.003727733160539266</v>
+        <v>0.006593395231482613</v>
       </c>
       <c r="BN11" t="n">
-        <v>21.76666666666667</v>
+        <v>7.7</v>
       </c>
       <c r="BO11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BP11" t="n">
-        <v>235.5333333333333</v>
+        <v>232.1666666666667</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6.467985386800186</v>
+        <v>5.732527755094208</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.01020685956904821</v>
+        <v>0.0100880667654506</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.005727123930450606</v>
+        <v>0.005669130952378976</v>
       </c>
       <c r="BT11" t="n">
-        <v>104.6666666666667</v>
+        <v>102.5333333333333</v>
       </c>
       <c r="BU11" t="n">
         <v>0</v>
@@ -3233,28 +3265,28 @@
         <v>89.23333333333333</v>
       </c>
       <c r="CK11" t="n">
+        <v>3</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>257.5333333333334</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0.8536779467645159</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0.03173059452041893</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0.01668907320645818</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ11" t="n">
         <v>2</v>
       </c>
-      <c r="CL11" t="n">
-        <v>264.5</v>
-      </c>
-      <c r="CM11" t="n">
-        <v>1.210793625501215</v>
-      </c>
-      <c r="CN11" t="n">
-        <v>0.0380174418844219</v>
-      </c>
-      <c r="CO11" t="n">
-        <v>0.01854345315963044</v>
-      </c>
-      <c r="CP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ11" t="n">
-        <v>4</v>
-      </c>
       <c r="CR11" t="n">
-        <v>38.8</v>
+        <v>28.23333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -3264,13 +3296,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23.5</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="C12" t="n">
-        <v>13.4</v>
+        <v>24.9</v>
       </c>
       <c r="D12" t="n">
-        <v>6.333333333333333</v>
+        <v>10.26666666666667</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -3279,34 +3311,34 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9666666666666667</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7333333333333333</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6333333333333333</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>41.03287024549347</v>
+        <v>40.81798736056876</v>
       </c>
       <c r="N12" t="n">
-        <v>0.03040421663155402</v>
+        <v>0.03054053401787071</v>
       </c>
       <c r="O12" t="n">
-        <v>0.01630715550112727</v>
+        <v>0.01634839343164074</v>
       </c>
       <c r="P12" t="n">
-        <v>68.46666666666667</v>
+        <v>66.3</v>
       </c>
       <c r="Q12" t="n">
         <v>20.91014878270322</v>
@@ -3342,7 +3374,7 @@
         <v>21</v>
       </c>
       <c r="AB12" t="n">
-        <v>210.2</v>
+        <v>201.9666666666667</v>
       </c>
       <c r="AC12" t="n">
         <v>16.88432621603047</v>
@@ -3381,16 +3413,16 @@
         <v>241.4666666666667</v>
       </c>
       <c r="AO12" t="n">
-        <v>5.089373462759409</v>
+        <v>5.030860496917924</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.01067567300906058</v>
+        <v>0.01065906742693978</v>
       </c>
       <c r="AQ12" t="n">
         <v>0.005444826464012564</v>
       </c>
       <c r="AR12" t="n">
-        <v>79.76666666666667</v>
+        <v>78.63333333333334</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
@@ -3462,16 +3494,16 @@
         <v>4</v>
       </c>
       <c r="BP12" t="n">
-        <v>265.0333333333334</v>
+        <v>261.5666666666667</v>
       </c>
       <c r="BQ12" t="n">
-        <v>7.857642038597536</v>
+        <v>7.749657225804933</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.0142145142633967</v>
+        <v>0.01439574982292058</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.006988454197666527</v>
+        <v>0.007141824582608813</v>
       </c>
       <c r="BT12" t="n">
         <v>37.6</v>
@@ -3492,7 +3524,7 @@
         <v>6</v>
       </c>
       <c r="BZ12" t="n">
-        <v>196.8666666666667</v>
+        <v>186.7333333333333</v>
       </c>
       <c r="CA12" t="n">
         <v>1.882407132815519</v>
@@ -3556,49 +3588,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9.566666666666666</v>
+        <v>11.9</v>
       </c>
       <c r="C13" t="n">
-        <v>3.333333333333333</v>
+        <v>6.266666666666667</v>
       </c>
       <c r="D13" t="n">
-        <v>2.933333333333333</v>
+        <v>5.633333333333334</v>
       </c>
       <c r="E13" t="n">
-        <v>9.633333333333333</v>
+        <v>10.8</v>
       </c>
       <c r="F13" t="n">
-        <v>1.566666666666667</v>
+        <v>3.033333333333333</v>
       </c>
       <c r="G13" t="n">
-        <v>4.1</v>
+        <v>7.766666666666667</v>
       </c>
       <c r="H13" t="n">
-        <v>4.566666666666666</v>
+        <v>6.2</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>1.733333333333333</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2.7</v>
+        <v>4.466666666666667</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>26.91320050729853</v>
+        <v>26.72216124356069</v>
       </c>
       <c r="N13" t="n">
-        <v>0.017040434171123</v>
+        <v>0.01707799029474955</v>
       </c>
       <c r="O13" t="n">
-        <v>0.009198265690375518</v>
+        <v>0.009210389476618008</v>
       </c>
       <c r="P13" t="n">
-        <v>220.4666666666667</v>
+        <v>217.1666666666667</v>
       </c>
       <c r="Q13" t="n">
         <v>9.887726146238267</v>
@@ -3670,7 +3702,7 @@
         <v>22</v>
       </c>
       <c r="AN13" t="n">
-        <v>522.5333333333333</v>
+        <v>507.9333333333333</v>
       </c>
       <c r="AO13" t="n">
         <v>6.820098044751968</v>
@@ -3757,13 +3789,13 @@
         <v>32.83333333333334</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.673151900170169</v>
+        <v>5.625712430049042</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.006523301539291149</v>
+        <v>0.006503612477994802</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.003174118658951119</v>
+        <v>0.003186407428923954</v>
       </c>
       <c r="BT13" t="n">
         <v>150.2333333333333</v>
@@ -3820,7 +3852,7 @@
         <v>3</v>
       </c>
       <c r="CL13" t="n">
-        <v>30.23333333333333</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
@@ -3848,22 +3880,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11.8</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>5.666666666666667</v>
+        <v>11.36666666666667</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5</v>
+        <v>8.633333333333333</v>
       </c>
       <c r="E14" t="n">
-        <v>11.56666666666667</v>
+        <v>13.06666666666667</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3</v>
+        <v>6.966666666666667</v>
       </c>
       <c r="G14" t="n">
-        <v>3.166666666666667</v>
+        <v>6.1</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -3872,7 +3904,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -3881,16 +3913,16 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>44.17075010321354</v>
+        <v>43.34336715034517</v>
       </c>
       <c r="N14" t="n">
-        <v>0.03474755581764866</v>
+        <v>0.03510535181979335</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01682233176107339</v>
+        <v>0.0171097856433281</v>
       </c>
       <c r="P14" t="n">
-        <v>134.8</v>
+        <v>130.3333333333333</v>
       </c>
       <c r="Q14" t="n">
         <v>18.28112617710056</v>
@@ -3905,28 +3937,28 @@
         <v>39.63333333333333</v>
       </c>
       <c r="U14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V14" t="n">
-        <v>211.8666666666667</v>
+        <v>208.2333333333333</v>
       </c>
       <c r="W14" t="n">
-        <v>31.08104775647137</v>
+        <v>30.62482762667445</v>
       </c>
       <c r="X14" t="n">
-        <v>0.03237889195483237</v>
+        <v>0.03354218350439221</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.01836944571799711</v>
+        <v>0.0190273946820222</v>
       </c>
       <c r="Z14" t="n">
-        <v>124.9</v>
+        <v>110.1333333333333</v>
       </c>
       <c r="AA14" t="n">
         <v>47</v>
       </c>
       <c r="AB14" t="n">
-        <v>451.8666666666667</v>
+        <v>438.4333333333333</v>
       </c>
       <c r="AC14" t="n">
         <v>16.871806458265</v>
@@ -3959,22 +3991,22 @@
         <v>26.46666666666667</v>
       </c>
       <c r="AM14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AN14" t="n">
-        <v>138</v>
+        <v>126.8</v>
       </c>
       <c r="AO14" t="n">
-        <v>13.69507077387263</v>
+        <v>13.65520195661423</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.02800794750512109</v>
+        <v>0.0291876720894102</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.01573538440246802</v>
+        <v>0.01646104899856438</v>
       </c>
       <c r="AR14" t="n">
-        <v>59.83333333333334</v>
+        <v>56.63333333333333</v>
       </c>
       <c r="AS14" t="n">
         <v>2.845283612399248</v>
@@ -4010,7 +4042,7 @@
         <v>9</v>
       </c>
       <c r="BD14" t="n">
-        <v>149.3666666666667</v>
+        <v>144.0666666666667</v>
       </c>
       <c r="BE14" t="n">
         <v>7.942871028634748</v>
@@ -4049,13 +4081,13 @@
         <v>69.03333333333333</v>
       </c>
       <c r="BQ14" t="n">
-        <v>9.088178788705587</v>
+        <v>9.028926912499568</v>
       </c>
       <c r="BR14" t="n">
         <v>0.01128778271728081</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.005794829552597358</v>
+        <v>0.005590909615548978</v>
       </c>
       <c r="BT14" t="n">
         <v>71.13333333333334</v>
@@ -4076,7 +4108,7 @@
         <v>6</v>
       </c>
       <c r="BZ14" t="n">
-        <v>113.9333333333333</v>
+        <v>110.4</v>
       </c>
       <c r="CA14" t="n">
         <v>4.854215821628155</v>
@@ -4140,31 +4172,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.433333333333333</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>7.366666666666666</v>
+        <v>9.433333333333334</v>
       </c>
       <c r="F15" t="n">
-        <v>3.633333333333333</v>
+        <v>6.966666666666667</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>2.466666666666667</v>
       </c>
       <c r="H15" t="n">
-        <v>2.633333333333333</v>
+        <v>2.9</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -4257,16 +4289,16 @@
         <v>239.4666666666667</v>
       </c>
       <c r="AO15" t="n">
-        <v>11.00497636861314</v>
+        <v>10.98193879460541</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.01716045744176153</v>
+        <v>0.01770651912122356</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.008963174793581885</v>
+        <v>0.00918316591486934</v>
       </c>
       <c r="AR15" t="n">
-        <v>71.7</v>
+        <v>68.5</v>
       </c>
       <c r="AS15" t="n">
         <v>3.778322902697958</v>
@@ -4338,13 +4370,13 @@
         <v>7</v>
       </c>
       <c r="BP15" t="n">
-        <v>59.46666666666667</v>
+        <v>55.8</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.936760625986645</v>
+        <v>6.825535828549514</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.01024740347457864</v>
+        <v>0.01020748476350175</v>
       </c>
       <c r="BS15" t="n">
         <v>0.005652700496896035</v>
@@ -4401,28 +4433,28 @@
         <v>34.76666666666667</v>
       </c>
       <c r="CK15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CL15" t="n">
-        <v>118.8333333333333</v>
+        <v>118.3333333333333</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.977890006876402</v>
+        <v>1.13806308309163</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.008477926696104912</v>
+        <v>0.009184620569627185</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.004254344819303737</v>
+        <v>0.004189253031503921</v>
       </c>
       <c r="CP15" t="n">
-        <v>74.16666666666666</v>
+        <v>24</v>
       </c>
       <c r="CQ15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CR15" t="n">
-        <v>141.2666666666667</v>
+        <v>140.1333333333333</v>
       </c>
     </row>
     <row r="16">
@@ -4432,34 +4464,34 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>37.16666666666666</v>
+        <v>46.23333333333333</v>
       </c>
       <c r="C16" t="n">
-        <v>10.66666666666667</v>
+        <v>18.93333333333333</v>
       </c>
       <c r="D16" t="n">
-        <v>14.9</v>
+        <v>27.3</v>
       </c>
       <c r="E16" t="n">
-        <v>5.733333333333333</v>
+        <v>6.4</v>
       </c>
       <c r="F16" t="n">
-        <v>1.466666666666667</v>
+        <v>2.933333333333333</v>
       </c>
       <c r="G16" t="n">
-        <v>2.166666666666667</v>
+        <v>3.466666666666667</v>
       </c>
       <c r="H16" t="n">
-        <v>1.733333333333333</v>
+        <v>1.9</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.166666666666667</v>
+        <v>1.9</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -4549,16 +4581,16 @@
         <v>112.8333333333333</v>
       </c>
       <c r="AO16" t="n">
-        <v>10.30840477443927</v>
+        <v>10.14020417981883</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.01462981412087605</v>
+        <v>0.01467644429011639</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.007298827238081951</v>
+        <v>0.007654804889134503</v>
       </c>
       <c r="AR16" t="n">
-        <v>41.83333333333334</v>
+        <v>39.63333333333333</v>
       </c>
       <c r="AS16" t="n">
         <v>2.80762575932226</v>
@@ -4594,7 +4626,7 @@
         <v>7</v>
       </c>
       <c r="BD16" t="n">
-        <v>37.3</v>
+        <v>28.43333333333333</v>
       </c>
       <c r="BE16" t="n">
         <v>4.14119564858145</v>
@@ -4633,16 +4665,16 @@
         <v>37.93333333333333</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7.006719941581409</v>
+        <v>6.98718493389618</v>
       </c>
       <c r="BR16" t="n">
-        <v>0.008249359486796504</v>
+        <v>0.008285000837294387</v>
       </c>
       <c r="BS16" t="n">
-        <v>0.003403730304632036</v>
+        <v>0.003394746406254923</v>
       </c>
       <c r="BT16" t="n">
-        <v>101.4333333333333</v>
+        <v>99.93333333333334</v>
       </c>
       <c r="BU16" t="n">
         <v>1.886154189725425</v>
@@ -4696,7 +4728,7 @@
         <v>5</v>
       </c>
       <c r="CL16" t="n">
-        <v>134.2</v>
+        <v>131.8</v>
       </c>
       <c r="CM16" t="n">
         <v>0.3421133472325515</v>
@@ -4724,46 +4756,46 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24.7</v>
+        <v>40.13333333333333</v>
       </c>
       <c r="C17" t="n">
-        <v>15.13333333333333</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="D17" t="n">
-        <v>6.4</v>
+        <v>10.96666666666667</v>
       </c>
       <c r="E17" t="n">
+        <v>3.866666666666667</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.866666666666667</v>
+      </c>
+      <c r="H17" t="n">
         <v>2.366666666666667</v>
       </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1.833333333333333</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.2</v>
-      </c>
       <c r="I17" t="n">
-        <v>0.2666666666666667</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4</v>
+        <v>2.366666666666667</v>
       </c>
       <c r="L17" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>70.2344094477498</v>
+        <v>69.71567141877861</v>
       </c>
       <c r="N17" t="n">
-        <v>0.05601746701610444</v>
+        <v>0.05633000598096144</v>
       </c>
       <c r="O17" t="n">
-        <v>0.02778105016777188</v>
+        <v>0.02818473635890639</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -4817,10 +4849,10 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AH17" t="n">
-        <v>340.9666666666666</v>
+        <v>338.9666666666666</v>
       </c>
       <c r="AI17" t="n">
         <v>34.52437464314256</v>
@@ -4835,19 +4867,19 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="AN17" t="n">
-        <v>382.2</v>
+        <v>373.6</v>
       </c>
       <c r="AO17" t="n">
-        <v>12.08032494182207</v>
+        <v>11.12631200710782</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.02199440561833765</v>
+        <v>0.02162807713282106</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.009577335921961971</v>
+        <v>0.009486880615243942</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4922,37 +4954,37 @@
         <v>8</v>
       </c>
       <c r="BP17" t="n">
-        <v>245.8333333333333</v>
+        <v>221.4</v>
       </c>
       <c r="BQ17" t="n">
-        <v>25.87634772887779</v>
+        <v>22.50339623859954</v>
       </c>
       <c r="BR17" t="n">
-        <v>0.02852828173523503</v>
+        <v>0.02777326442263989</v>
       </c>
       <c r="BS17" t="n">
-        <v>0.01597347682425321</v>
+        <v>0.01573606214901102</v>
       </c>
       <c r="BT17" t="n">
         <v>0</v>
       </c>
       <c r="BU17" t="n">
-        <v>15.86007977593245</v>
+        <v>4.439349781648632</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.02651185179895799</v>
+        <v>0.02854054442015375</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.03119998911157157</v>
+        <v>0.01431056453399082</v>
       </c>
       <c r="BX17" t="n">
         <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BZ17" t="n">
-        <v>13.6</v>
+        <v>8.4</v>
       </c>
       <c r="CA17" t="n">
         <v>3.955070269295267</v>
@@ -4967,37 +4999,37 @@
         <v>0</v>
       </c>
       <c r="CE17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CF17" t="n">
-        <v>65.26666666666667</v>
+        <v>60.93333333333333</v>
       </c>
       <c r="CG17" t="n">
-        <v>7.618457990334736</v>
+        <v>5.441345090270231</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.04045171540944004</v>
+        <v>0.03885489640768517</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.08019161251017544</v>
+        <v>0.02153831918018531</v>
       </c>
       <c r="CJ17" t="n">
         <v>0</v>
       </c>
       <c r="CK17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="CL17" t="n">
-        <v>41.36666666666667</v>
+        <v>39.23333333333333</v>
       </c>
       <c r="CM17" t="n">
-        <v>14.62256601073568</v>
+        <v>10.81637286553214</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.02352312028245483</v>
+        <v>0.02318718244358459</v>
       </c>
       <c r="CO17" t="n">
-        <v>0.01852558316204763</v>
+        <v>0.01744023811919047</v>
       </c>
       <c r="CP17" t="n">
         <v>0</v>
@@ -5006,7 +5038,7 @@
         <v>10</v>
       </c>
       <c r="CR17" t="n">
-        <v>191.1333333333333</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18">
@@ -5016,46 +5048,46 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20.73333333333333</v>
+        <v>33.36666666666667</v>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>21.43333333333333</v>
       </c>
       <c r="D18" t="n">
-        <v>6.8</v>
+        <v>11.93333333333333</v>
       </c>
       <c r="E18" t="n">
-        <v>3.366666666666667</v>
+        <v>3.8</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H18" t="n">
+        <v>7.233333333333333</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.033333333333333</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>2.266666666666667</v>
       </c>
-      <c r="H18" t="n">
-        <v>7.633333333333334</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2.566666666666667</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1.366666666666667</v>
-      </c>
       <c r="L18" t="n">
-        <v>2.333333333333333</v>
+        <v>1.933333333333333</v>
       </c>
       <c r="M18" t="n">
-        <v>49.88938775957637</v>
+        <v>49.43863511150209</v>
       </c>
       <c r="N18" t="n">
         <v>0.0400376406211681</v>
       </c>
       <c r="O18" t="n">
-        <v>0.02042088211463366</v>
+        <v>0.02029345348367229</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -5094,7 +5126,7 @@
         <v>21</v>
       </c>
       <c r="AB18" t="n">
-        <v>54.7</v>
+        <v>49.5</v>
       </c>
       <c r="AC18" t="n">
         <v>24.65154568921367</v>
@@ -5133,13 +5165,13 @@
         <v>449.0333333333334</v>
       </c>
       <c r="AO18" t="n">
-        <v>14.24468668167495</v>
+        <v>13.80625979384615</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.0282545569130509</v>
+        <v>0.02861556212431127</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.01234475467806406</v>
+        <v>0.01231628775670335</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -5181,70 +5213,70 @@
         <v>27.46666666666667</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.663175280213705</v>
+        <v>5.219708255067102</v>
       </c>
       <c r="BF18" t="n">
-        <v>0.0369201199149163</v>
+        <v>0.03615303390062379</v>
       </c>
       <c r="BG18" t="n">
-        <v>0.01779635869756592</v>
+        <v>0.01569445370837852</v>
       </c>
       <c r="BH18" t="n">
         <v>0</v>
       </c>
       <c r="BI18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>9.119873788401428</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0.02634064875671116</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0.01037657609574772</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO18" t="n">
         <v>9</v>
       </c>
-      <c r="BJ18" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>9.28040784107348</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>0.02623030350766159</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>0.01038899724898121</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>10</v>
-      </c>
       <c r="BP18" t="n">
-        <v>201.5</v>
+        <v>190.7</v>
       </c>
       <c r="BQ18" t="n">
-        <v>94.22810407385174</v>
+        <v>88.01746034736119</v>
       </c>
       <c r="BR18" t="n">
-        <v>0.06712900375967926</v>
+        <v>0.0667269256760869</v>
       </c>
       <c r="BS18" t="n">
-        <v>0.04697947100619004</v>
+        <v>0.04606023034590562</v>
       </c>
       <c r="BT18" t="n">
         <v>0</v>
       </c>
       <c r="BU18" t="n">
-        <v>43.89314634063432</v>
+        <v>36.51962201057744</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.05909055908769315</v>
+        <v>0.0586210566217687</v>
       </c>
       <c r="BW18" t="n">
-        <v>0.06530739700346884</v>
+        <v>0.04430076611421622</v>
       </c>
       <c r="BX18" t="n">
         <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BZ18" t="n">
-        <v>44.76666666666667</v>
+        <v>39.93333333333333</v>
       </c>
       <c r="CA18" t="n">
         <v>38.71992980858501</v>
@@ -5259,46 +5291,46 @@
         <v>0</v>
       </c>
       <c r="CE18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CF18" t="n">
-        <v>70.3</v>
+        <v>68.7</v>
       </c>
       <c r="CG18" t="n">
-        <v>14.82884616756616</v>
+        <v>11.41521229492442</v>
       </c>
       <c r="CH18" t="n">
-        <v>0.04973045082337421</v>
+        <v>0.0463583916563854</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.1185424472765765</v>
+        <v>0.09401042656823357</v>
       </c>
       <c r="CJ18" t="n">
         <v>0</v>
       </c>
       <c r="CK18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CL18" t="n">
-        <v>91.03333333333333</v>
+        <v>88.96666666666667</v>
       </c>
       <c r="CM18" t="n">
-        <v>63.20978312272279</v>
+        <v>57.53899285017107</v>
       </c>
       <c r="CN18" t="n">
-        <v>0.06532953549714633</v>
+        <v>0.06902143293161349</v>
       </c>
       <c r="CO18" t="n">
-        <v>0.1701204330144373</v>
+        <v>0.1849333248251371</v>
       </c>
       <c r="CP18" t="n">
         <v>0</v>
       </c>
       <c r="CQ18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CR18" t="n">
-        <v>93.3</v>
+        <v>92.86666666666666</v>
       </c>
     </row>
     <row r="19">
@@ -5308,46 +5340,46 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>45.8</v>
+        <v>76.53333333333333</v>
       </c>
       <c r="C19" t="n">
-        <v>25</v>
+        <v>47.73333333333333</v>
       </c>
       <c r="D19" t="n">
-        <v>16.1</v>
+        <v>28.8</v>
       </c>
       <c r="E19" t="n">
-        <v>17.7</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="F19" t="n">
-        <v>6.533333333333333</v>
+        <v>11</v>
       </c>
       <c r="G19" t="n">
-        <v>9</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="H19" t="n">
-        <v>19.96666666666667</v>
+        <v>31.63333333333333</v>
       </c>
       <c r="I19" t="n">
-        <v>1.633333333333333</v>
+        <v>3.533333333333333</v>
       </c>
       <c r="J19" t="n">
-        <v>3.766666666666667</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>7.833333333333333</v>
+        <v>16</v>
       </c>
       <c r="L19" t="n">
-        <v>2.7</v>
+        <v>5.433333333333334</v>
       </c>
       <c r="M19" t="n">
-        <v>66.59960688623011</v>
+        <v>66.46680148220914</v>
       </c>
       <c r="N19" t="n">
-        <v>0.06003087382854988</v>
+        <v>0.06020350697876847</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0315795042141282</v>
+        <v>0.031573868747516</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -5368,7 +5400,7 @@
         <v>32</v>
       </c>
       <c r="V19" t="n">
-        <v>110</v>
+        <v>109.5</v>
       </c>
       <c r="W19" t="n">
         <v>39.29879238827746</v>
@@ -5401,10 +5433,10 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AH19" t="n">
-        <v>121.2333333333333</v>
+        <v>119.3666666666667</v>
       </c>
       <c r="AI19" t="n">
         <v>45.085010121477</v>
@@ -5425,10 +5457,10 @@
         <v>504.7666666666667</v>
       </c>
       <c r="AO19" t="n">
-        <v>20.78393083979571</v>
+        <v>19.82363066320518</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.05538637774686689</v>
+        <v>0.05631655592646295</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.02707389316262077</v>
@@ -5473,46 +5505,46 @@
         <v>59.33333333333334</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.43985015518172</v>
+        <v>8.123398620057866</v>
       </c>
       <c r="BF19" t="n">
-        <v>0.06490343789561308</v>
+        <v>0.06595827065482608</v>
       </c>
       <c r="BG19" t="n">
-        <v>0.03125727549973099</v>
+        <v>0.0325181648522603</v>
       </c>
       <c r="BH19" t="n">
         <v>0</v>
       </c>
       <c r="BI19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BJ19" t="n">
-        <v>65.13333333333334</v>
+        <v>62.9</v>
       </c>
       <c r="BK19" t="n">
-        <v>10.2606366731543</v>
+        <v>9.733924694556388</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.04487489021806128</v>
+        <v>0.04667066006334736</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.02602085533292087</v>
+        <v>0.02620686313980776</v>
       </c>
       <c r="BN19" t="n">
-        <v>3.233333333333333</v>
+        <v>0</v>
       </c>
       <c r="BO19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BP19" t="n">
-        <v>156.7</v>
+        <v>143.7333333333333</v>
       </c>
       <c r="BQ19" t="n">
-        <v>91.61897823815885</v>
+        <v>91.45158289125622</v>
       </c>
       <c r="BR19" t="n">
-        <v>0.05316684628636548</v>
+        <v>0.05401004775485108</v>
       </c>
       <c r="BS19" t="n">
         <v>0.04466759908964268</v>
@@ -5554,7 +5586,7 @@
         <v>18</v>
       </c>
       <c r="CF19" t="n">
-        <v>74.86666666666666</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="CG19" t="n">
         <v>35.06623989721712</v>
@@ -5600,46 +5632,46 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.166666666666667</v>
+        <v>10.26666666666667</v>
       </c>
       <c r="C20" t="n">
-        <v>3.133333333333333</v>
+        <v>4.066666666666666</v>
       </c>
       <c r="D20" t="n">
-        <v>3.133333333333333</v>
+        <v>6.2</v>
       </c>
       <c r="E20" t="n">
-        <v>3.333333333333333</v>
+        <v>5</v>
       </c>
       <c r="F20" t="n">
-        <v>1.033333333333333</v>
+        <v>2.5</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="H20" t="n">
-        <v>1.333333333333333</v>
+        <v>2.633333333333333</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1.166666666666667</v>
+        <v>2.633333333333333</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>44.40104541601987</v>
+        <v>44.22172404085659</v>
       </c>
       <c r="N20" t="n">
-        <v>0.03476501907927798</v>
+        <v>0.03488550824290004</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0157387512171448</v>
+        <v>0.01569755492785685</v>
       </c>
       <c r="P20" t="n">
         <v>1.033333333333333</v>
@@ -5714,16 +5746,16 @@
         <v>29</v>
       </c>
       <c r="AN20" t="n">
-        <v>515.2666666666667</v>
+        <v>509.9666666666666</v>
       </c>
       <c r="AO20" t="n">
-        <v>10.65063152566757</v>
+        <v>9.780319334330137</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.01820632370396735</v>
+        <v>0.01767756793008268</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.007062233632339598</v>
+        <v>0.006663294043291135</v>
       </c>
       <c r="AR20" t="n">
         <v>1.033333333333333</v>
@@ -5780,7 +5812,7 @@
         <v>4</v>
       </c>
       <c r="BJ20" t="n">
-        <v>19.03333333333333</v>
+        <v>18.43333333333333</v>
       </c>
       <c r="BK20" t="n">
         <v>6.125183269057723</v>
@@ -5795,19 +5827,19 @@
         <v>1.033333333333333</v>
       </c>
       <c r="BO20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BP20" t="n">
-        <v>279.2666666666667</v>
+        <v>267.5</v>
       </c>
       <c r="BQ20" t="n">
-        <v>32.35893481904742</v>
+        <v>25.13368329391714</v>
       </c>
       <c r="BR20" t="n">
-        <v>0.01446520054012868</v>
+        <v>0.013954715341156</v>
       </c>
       <c r="BS20" t="n">
-        <v>0.005262967941807806</v>
+        <v>0.00510611475388556</v>
       </c>
       <c r="BT20" t="n">
         <v>6.333333333333333</v>
@@ -5825,10 +5857,10 @@
         <v>0</v>
       </c>
       <c r="BY20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BZ20" t="n">
-        <v>13.36666666666667</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="CA20" t="n">
         <v>9.610835628106308</v>
@@ -5843,10 +5875,10 @@
         <v>0</v>
       </c>
       <c r="CE20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CF20" t="n">
-        <v>15.5</v>
+        <v>11.33333333333333</v>
       </c>
       <c r="CG20" t="n">
         <v>3.943351173178713</v>
@@ -5864,33 +5896,38 @@
         <v>5</v>
       </c>
       <c r="CL20" t="n">
-        <v>24.1</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="CM20" t="n">
-        <v>22.81801615735948</v>
+        <v>14.80059733779939</v>
       </c>
       <c r="CN20" t="n">
-        <v>0.03335949255687127</v>
+        <v>0.02310407879058406</v>
       </c>
       <c r="CO20" t="n">
-        <v>0.04825957707200994</v>
+        <v>0.03131717060223094</v>
       </c>
       <c r="CP20" t="n">
         <v>6.333333333333333</v>
       </c>
       <c r="CQ20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CR20" t="n">
-        <v>259.0666666666667</v>
+        <v>258.6333333333333</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="B1:L1"/>
+  <mergeCells count="24">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:L1"/>
     <mergeCell ref="M1:AN1"/>
     <mergeCell ref="AO1:BP1"/>
     <mergeCell ref="BQ1:CR1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:L2"/>
     <mergeCell ref="M2:P2"/>
     <mergeCell ref="Q2:V2"/>
     <mergeCell ref="W2:AB2"/>
